--- a/analysis/summary_hit_days_all.xlsx
+++ b/analysis/summary_hit_days_all.xlsx
@@ -508,34 +508,34 @@
         <v>52</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2115384615384615</v>
+        <v>0.3653846153846153</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.59375</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4523809523809523</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9780278670953912</v>
+        <v>0.9821331889550624</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00'), Timestamp('2021-12-06 00:00:00')]</t>
+          <t>[Timestamp('2021-11-19 00:00:00'), Timestamp('2021-11-23 00:00:00'), Timestamp('2021-11-29 00:00:00'), Timestamp('2021-12-06 00:00:00'), Timestamp('2021-12-17 00:00:00'), Timestamp('2021-12-21 00:00:00')]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-16 00:00:00'), Timestamp('2021-11-30 00:00:00')]</t>
+          <t>[Timestamp('2021-11-12 00:00:00'), Timestamp('2021-11-21 00:00:00'), Timestamp('2021-11-26 00:00:00'), Timestamp('2021-11-30 00:00:00'), Timestamp('2021-12-13 00:00:00'), Timestamp('2021-12-19 00:00:00')]</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -555,45 +555,45 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.2142857142857142</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.25</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2580645161290322</v>
+        <v>0.2307692307692307</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9893333333333332</v>
+        <v>0.9881529348411416</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00'), Timestamp('2021-12-06 00:00:00')]</t>
+          <t>[Timestamp('2021-12-17 00:00:00'), Timestamp('2021-12-21 00:00:00')]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-17 00:00:00'), Timestamp('2021-11-29 00:00:00')]</t>
+          <t>[Timestamp('2021-12-14 00:00:00'), Timestamp('2021-12-18 00:00:00')]</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.000311047954167</v>
+        <v>0.9991940067357143</v>
       </c>
     </row>
     <row r="4">
@@ -609,45 +609,45 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="n">
-        <v>7</v>
-      </c>
       <c r="H4" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.1621621621621621</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2033898305084745</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9882604055496264</v>
+        <v>0.983288409703504</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00')]</t>
+          <t>[Timestamp('2021-03-20 00:00:00'), Timestamp('2021-03-23 00:00:00'), Timestamp('2021-03-26 00:00:00'), Timestamp('2021-12-17 00:00:00'), Timestamp('2021-12-21 00:00:00')]</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-16 00:00:00')]</t>
+          <t>[Timestamp('2021-03-18 00:00:00'), Timestamp('2021-03-22 00:00:00'), Timestamp('2021-03-24 00:00:00'), Timestamp('2021-12-14 00:00:00'), Timestamp('2021-12-19 00:00:00')]</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.9991432546833332</v>
+        <v>0.9995264220135136</v>
       </c>
     </row>
     <row r="5">
@@ -663,45 +663,45 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7</v>
-      </c>
       <c r="H5" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1702127659574468</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9957310565635006</v>
+        <v>0.988691437802908</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00')]</t>
+          <t>[Timestamp('2021-11-19 00:00:00'), Timestamp('2021-12-17 00:00:00')]</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-16 00:00:00')]</t>
+          <t>[Timestamp('2021-11-12 00:00:00'), Timestamp('2021-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.999567863511111</v>
+        <v>0.999809069144</v>
       </c>
     </row>
     <row r="6">
@@ -717,41 +717,45 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.333333333333333</v>
+      </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2068965517241379</v>
+      </c>
       <c r="K6" t="n">
-        <v>0.985082578582845</v>
+        <v>0.9967672413793104</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-11-19 00:00:00'), Timestamp('2021-12-17 00:00:00'), Timestamp('2021-12-21 00:00:00')]</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-11-16 00:00:00'), Timestamp('2021-12-16 00:00:00'), Timestamp('2021-12-18 00:00:00')]</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.9991940067357143</v>
+        <v>0.999567863511111</v>
       </c>
     </row>
     <row r="7">
@@ -767,41 +771,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.5</v>
+      </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1142857142857143</v>
+      </c>
       <c r="K7" t="n">
-        <v>0.9866737739872068</v>
+        <v>0.9882163899303696</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-11-19 00:00:00'), Timestamp('2021-12-17 00:00:00')]</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-11-17 00:00:00'), Timestamp('2021-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.999809069144</v>
+        <v>1.000311047954167</v>
       </c>
     </row>
     <row r="8">
@@ -817,41 +825,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0909090909090909</v>
+      </c>
       <c r="K8" t="n">
-        <v>0.9834754797441364</v>
+        <v>0.9881593110871906</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-11-19 00:00:00')]</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-11-16 00:00:00')]</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.9990350182580646</v>
+        <v>0.9991432546833332</v>
       </c>
     </row>
     <row r="9">
@@ -867,41 +879,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.032258064516129</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
+        <v>0.0476190476190476</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0384615384615384</v>
+      </c>
       <c r="K9" t="n">
-        <v>0.980277185501066</v>
+        <v>0.9838536060279872</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-17 00:00:00')]</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.9995264220135136</v>
+        <v>0.9990350182580646</v>
       </c>
     </row>
     <row r="10">
@@ -924,30 +940,34 @@
         <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.032258064516129</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>0.0476190476190476</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0384615384615384</v>
+      </c>
       <c r="K10" t="n">
-        <v>0.9834754797441364</v>
+        <v>0.9838536060279872</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-17 00:00:00')]</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -974,7 +994,7 @@
         <v>23</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -988,7 +1008,7 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>0.9877398720682304</v>
+        <v>0.9876344086021506</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1024,34 +1044,34 @@
         <v>112</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
         <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>4.125</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="H12" t="n">
         <v>0.2410714285714285</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="J12" t="n">
-        <v>0.36</v>
+        <v>0.3483870967741935</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9540292049756626</v>
+        <v>0.9539544962080172</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-09 00:00:00'), Timestamp('2023-05-24 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-07-24 00:00:00'), Timestamp('2023-09-02 00:00:00'), Timestamp('2023-10-02 00:00:00'), Timestamp('2023-10-05 00:00:00'), Timestamp('2023-12-16 00:00:00')]</t>
+          <t>[Timestamp('2022-11-29 00:00:00'), Timestamp('2023-03-09 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-05-24 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-07-19 00:00:00'), Timestamp('2023-07-21 00:00:00'), Timestamp('2023-07-24 00:00:00'), Timestamp('2023-09-22 00:00:00'), Timestamp('2023-09-29 00:00:00'), Timestamp('2023-10-05 00:00:00'), Timestamp('2023-12-16 00:00:00')]</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-07 00:00:00'), Timestamp('2023-05-18 00:00:00'), Timestamp('2023-07-07 00:00:00'), Timestamp('2023-07-17 00:00:00'), Timestamp('2023-09-01 00:00:00'), Timestamp('2023-09-25 00:00:00'), Timestamp('2023-10-03 00:00:00'), Timestamp('2023-12-15 00:00:00')]</t>
+          <t>[Timestamp('2022-11-28 00:00:00'), Timestamp('2023-03-07 00:00:00'), Timestamp('2023-05-18 00:00:00'), Timestamp('2023-05-20 00:00:00'), Timestamp('2023-07-07 00:00:00'), Timestamp('2023-07-15 00:00:00'), Timestamp('2023-07-20 00:00:00'), Timestamp('2023-07-22 00:00:00'), Timestamp('2023-09-18 00:00:00'), Timestamp('2023-09-24 00:00:00'), Timestamp('2023-10-03 00:00:00'), Timestamp('2023-12-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1071,45 +1091,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>113</v>
       </c>
       <c r="E13" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6</v>
+        <v>4.714285714285714</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0619469026548672</v>
+        <v>0.1238938053097345</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1021897810218978</v>
+        <v>0.1842105263157894</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9428263214670982</v>
+        <v>0.9463123644251626</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-05-24 00:00:00'), Timestamp('2023-07-14 00:00:00')]</t>
+          <t>[Timestamp('2022-11-29 00:00:00'), Timestamp('2023-03-09 00:00:00'), Timestamp('2023-06-22 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-08-18 00:00:00'), Timestamp('2023-09-01 00:00:00'), Timestamp('2023-09-22 00:00:00')]</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-08 00:00:00'), Timestamp('2023-04-14 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-05-17 00:00:00'), Timestamp('2023-07-11 00:00:00')]</t>
+          <t>[Timestamp('2022-11-23 00:00:00'), Timestamp('2023-03-02 00:00:00'), Timestamp('2023-06-15 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-08-17 00:00:00'), Timestamp('2023-08-29 00:00:00'), Timestamp('2023-09-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.9976027893238938</v>
+        <v>1.001409282890265</v>
       </c>
     </row>
     <row r="14">
@@ -1125,45 +1145,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0520833333333333</v>
+        <v>0.1061946902654867</v>
       </c>
       <c r="I14" t="n">
-        <v>0.217391304347826</v>
+        <v>0.3243243243243243</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0840336134453781</v>
+        <v>0.16</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9509433962264152</v>
+        <v>0.9450489662676824</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-09 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-03 00:00:00'), Timestamp('2023-06-29 00:00:00'), Timestamp('2023-07-10 00:00:00'), Timestamp('2023-12-11 00:00:00')]</t>
+          <t>[Timestamp('2023-04-14 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-05-12 00:00:00'), Timestamp('2023-07-11 00:00:00'), Timestamp('2024-06-28 00:00:00')]</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.9994954554343752</v>
+        <v>0.9976027893238938</v>
       </c>
     </row>
     <row r="15">
@@ -1179,45 +1199,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.1041666666666666</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="J15" t="n">
-        <v>0.08130081300813</v>
+        <v>0.150375939849624</v>
       </c>
       <c r="K15" t="n">
-        <v>0.949353448275862</v>
+        <v>0.9532100108813928</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-08-18 00:00:00'), Timestamp('2023-10-02 00:00:00')]</t>
+          <t>[Timestamp('2022-11-29 00:00:00'), Timestamp('2023-03-09 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-06-22 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-08 00:00:00'), Timestamp('2023-04-15 00:00:00'), Timestamp('2023-08-11 00:00:00'), Timestamp('2023-09-25 00:00:00')]</t>
+          <t>[Timestamp('2022-11-24 00:00:00'), Timestamp('2023-03-03 00:00:00'), Timestamp('2023-05-12 00:00:00'), Timestamp('2023-06-19 00:00:00'), Timestamp('2023-06-29 00:00:00'), Timestamp('2023-07-10 00:00:00'), Timestamp('2023-12-11 00:00:00')]</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.999974114</v>
+        <v>0.9994954554343752</v>
       </c>
     </row>
     <row r="16">
@@ -1240,34 +1260,34 @@
         <v>102</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>4.666666666666667</v>
+        <v>6.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0490196078431372</v>
+        <v>0.088235294117647</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>0.2368421052631578</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0787401574803149</v>
+        <v>0.1285714285714286</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9477088948787062</v>
+        <v>0.9494839760999456</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-09 00:00:00'), Timestamp('2023-05-24 00:00:00'), Timestamp('2023-07-14 00:00:00')]</t>
+          <t>[Timestamp('2023-05-19 00:00:00'), Timestamp('2023-07-14 00:00:00')]</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-08 00:00:00'), Timestamp('2023-05-17 00:00:00'), Timestamp('2023-07-08 00:00:00')]</t>
+          <t>[Timestamp('2023-05-12 00:00:00'), Timestamp('2023-07-08 00:00:00')]</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -1287,45 +1307,45 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="E17" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0442477876106194</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2272727272727272</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="J17" t="n">
-        <v>0.074074074074074</v>
+        <v>0.1025641025641025</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9419666845781838</v>
+        <v>0.9576547231270358</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-09 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-08-18 00:00:00'), Timestamp('2023-09-02 00:00:00')]</t>
+          <t>[Timestamp('2023-05-04 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-06-22 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-07-19 00:00:00')]</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-02 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-08-17 00:00:00'), Timestamp('2023-08-29 00:00:00')]</t>
+          <t>[Timestamp('2023-05-03 00:00:00'), Timestamp('2023-05-14 00:00:00'), Timestamp('2023-06-19 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-07-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.001409282890265</v>
+        <v>0.9994915789166668</v>
       </c>
     </row>
     <row r="18">
@@ -1341,45 +1361,45 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="E18" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0404040404040404</v>
+        <v>0.0806451612903225</v>
       </c>
       <c r="I18" t="n">
-        <v>0.16</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="J18" t="n">
-        <v>0.06451612903225799</v>
+        <v>0.1030927835051546</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9487870619946092</v>
+        <v>0.9690217391304348</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-07-24 00:00:00')]</t>
+          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-06-22 00:00:00'), Timestamp('2023-07-03 00:00:00')]</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-07-20 00:00:00')]</t>
+          <t>[Timestamp('2021-04-13 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-05-14 00:00:00'), Timestamp('2023-06-19 00:00:00'), Timestamp('2023-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.999888115441414</v>
+        <v>0.9997565723903226</v>
       </c>
     </row>
     <row r="19">
@@ -1395,45 +1415,45 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="E19" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>2.333333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0483870967741935</v>
+        <v>0.0505050505050505</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0705882352941176</v>
+        <v>0.0746268656716417</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9681769147788564</v>
+        <v>0.9489962018448184</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-03 00:00:00')]</t>
+          <t>[Timestamp('2023-05-19 00:00:00'), Timestamp('2023-06-22 00:00:00'), Timestamp('2023-07-21 00:00:00'), Timestamp('2023-07-24 00:00:00')]</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-13 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-07-01 00:00:00')]</t>
+          <t>[Timestamp('2023-05-14 00:00:00'), Timestamp('2023-06-19 00:00:00'), Timestamp('2023-07-20 00:00:00'), Timestamp('2023-07-22 00:00:00')]</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0.9997565723903226</v>
+        <v>0.999888115441414</v>
       </c>
     </row>
     <row r="20">
@@ -1449,45 +1469,45 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="E20" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>1.333333333333333</v>
+        <v>5.25</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0357142857142857</v>
+        <v>0.0505050505050505</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0560747663551401</v>
+        <v>0.0757575757575757</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9563577586206896</v>
+        <v>0.9490514905149052</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-09 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-03 00:00:00')]</t>
+          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-06-22 00:00:00'), Timestamp('2023-08-18 00:00:00'), Timestamp('2023-09-29 00:00:00')]</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-08 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-07-01 00:00:00')]</t>
+          <t>[Timestamp('2023-04-15 00:00:00'), Timestamp('2023-06-17 00:00:00'), Timestamp('2023-08-11 00:00:00'), Timestamp('2023-09-25 00:00:00')]</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.9994915789166668</v>
+        <v>0.999974114</v>
       </c>
     </row>
     <row r="21">
@@ -1510,7 +1530,7 @@
         <v>76</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1524,7 +1544,7 @@
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>0.959073774905762</v>
+        <v>0.9588075880758808</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1553,41 +1573,45 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.666666666666667</v>
+      </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.2978723404255319</v>
+      </c>
       <c r="K22" t="n">
-        <v>0.9941489361702128</v>
+        <v>0.9945770065075922</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-06-26 00:00:00'), Timestamp('2021-12-05 00:00:00'), Timestamp('2023-03-20 00:00:00')]</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-06-22 00:00:00'), Timestamp('2021-12-03 00:00:00'), Timestamp('2023-03-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.9978502162727272</v>
+        <v>1.000412956288235</v>
       </c>
     </row>
     <row r="23">
@@ -1603,41 +1627,45 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.5</v>
+      </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.1944444444444444</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>0.21875</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.2058823529411765</v>
+      </c>
       <c r="K23" t="n">
-        <v>0.988817891373802</v>
+        <v>0.9842988630211154</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-01-26 00:00:00'), Timestamp('2023-03-20 00:00:00')]</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-01-21 00:00:00'), Timestamp('2023-03-14 00:00:00')]</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.001134638261905</v>
+        <v>0.999634056236111</v>
       </c>
     </row>
     <row r="24">
@@ -1653,41 +1681,45 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E24" t="n">
+        <v>32</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
         <v>3</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.1754385964912281</v>
+      </c>
       <c r="K24" t="n">
-        <v>0.9808306709265175</v>
+        <v>0.9848320693391116</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-03-19 00:00:00'), Timestamp('2021-04-03 00:00:00'), Timestamp('2021-04-06 00:00:00'), Timestamp('2021-04-09 00:00:00'), Timestamp('2021-06-26 00:00:00')]</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-03-18 00:00:00'), Timestamp('2021-03-27 00:00:00'), Timestamp('2021-04-05 00:00:00'), Timestamp('2021-04-08 00:00:00'), Timestamp('2021-06-21 00:00:00')]</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.999634056236111</v>
+        <v>0.999798528460606</v>
       </c>
     </row>
     <row r="25">
@@ -1703,41 +1735,45 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.666666666666667</v>
+      </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.1538461538461538</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.1481481481481481</v>
+      </c>
       <c r="K25" t="n">
-        <v>0.987220447284345</v>
+        <v>0.988095238095238</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-03-19 00:00:00'), Timestamp('2022-01-26 00:00:00'), Timestamp('2023-03-20 00:00:00')]</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-03-18 00:00:00'), Timestamp('2022-01-21 00:00:00'), Timestamp('2023-03-18 00:00:00')]</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0.9998803603874999</v>
+        <v>0.999566539453846</v>
       </c>
     </row>
     <row r="26">
@@ -1753,41 +1789,45 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
+        <v>32</v>
+      </c>
+      <c r="F26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
+        <v>0.1153846153846153</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.1621621621621621</v>
+      </c>
       <c r="K26" t="n">
-        <v>0.9824281150159744</v>
+        <v>0.995682676740421</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-20 00:00:00')]</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-14 00:00:00')]</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.999798528460606</v>
+        <v>0.9978502162727272</v>
       </c>
     </row>
     <row r="27">
@@ -1803,41 +1843,45 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
+        <v>32</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.0909090909090909</v>
+      </c>
       <c r="K27" t="n">
-        <v>0.9840255591054312</v>
+        <v>0.9935100054083288</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-10 00:00:00'), Timestamp('2023-03-20 00:00:00')]</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-06 00:00:00'), Timestamp('2023-03-18 00:00:00')]</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0.9995894625066664</v>
+        <v>0.9992087907928572</v>
       </c>
     </row>
     <row r="28">
@@ -1853,41 +1897,45 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.09523809523809521</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>0.0869565217391304</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.0909090909090909</v>
+      </c>
       <c r="K28" t="n">
-        <v>0.9861554845580404</v>
+        <v>0.9897574123989218</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-03-22 00:00:00'), Timestamp('2023-03-20 00:00:00')]</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-03-21 00:00:00'), Timestamp('2023-03-18 00:00:00')]</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.999566539453846</v>
+        <v>1.001134638261905</v>
       </c>
     </row>
     <row r="29">
@@ -1903,41 +1951,45 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
+        <v>0.06451612903225799</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.06349206349206341</v>
+      </c>
       <c r="K29" t="n">
-        <v>0.992545260915868</v>
+        <v>0.9837837837837838</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-20 00:00:00')]</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-18 00:00:00')]</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0.9992087907928572</v>
+        <v>0.9994469989531251</v>
       </c>
     </row>
     <row r="30">
@@ -1953,41 +2005,45 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D30" t="n">
+        <v>30</v>
+      </c>
+      <c r="E30" t="n">
         <v>32</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
         <v>3</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
+        <v>0.0344827586206896</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0338983050847457</v>
+      </c>
       <c r="K30" t="n">
-        <v>0.9829605963791268</v>
+        <v>0.984332793084819</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-06-18 00:00:00')]</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-06-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.9994469989531251</v>
+        <v>0.9995894625066664</v>
       </c>
     </row>
     <row r="31">
@@ -2003,14 +2059,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2024,7 +2080,7 @@
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
-        <v>0.9909429941395844</v>
+        <v>0.987027027027027</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2037,7 +2093,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.000412956288235</v>
+        <v>0.9998803603874999</v>
       </c>
     </row>
     <row r="32">
@@ -2053,45 +2109,45 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0555555555555555</v>
+        <v>0.2</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J32" t="n">
-        <v>0.09999999999999989</v>
+        <v>0.2</v>
       </c>
       <c r="K32" t="n">
-        <v>0.9909478168264112</v>
+        <v>0.9870550161812298</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2022-05-11 00:00:00'), Timestamp('2025-01-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-10 00:00:00')]</t>
+          <t>[Timestamp('2022-05-09 00:00:00'), Timestamp('2024-12-28 00:00:00')]</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.001831838905556</v>
+        <v>0.9987720301766668</v>
       </c>
     </row>
     <row r="33">
@@ -2107,45 +2163,45 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>32</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
-        <v>0.03125</v>
+        <v>0.1875</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0588235294117647</v>
+        <v>0.2142857142857142</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9834842834310068</v>
+        <v>0.985968699406368</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-17 00:00:00')]</t>
+          <t>[Timestamp('2022-05-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-14 00:00:00')]</t>
+          <t>[Timestamp('2022-05-05 00:00:00')]</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.00091165069375</v>
+        <v>1.00066815294375</v>
       </c>
     </row>
     <row r="34">
@@ -2161,41 +2217,45 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.75</v>
+      </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.1785714285714285</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.2127659574468085</v>
+      </c>
       <c r="K34" t="n">
-        <v>0.9867021276595744</v>
+        <v>0.9875876956287102</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-04-11 00:00:00'), Timestamp('2022-11-10 00:00:00'), Timestamp('2024-03-08 00:00:00'), Timestamp('2024-12-05 00:00:00')]</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-04-05 00:00:00'), Timestamp('2022-11-08 00:00:00'), Timestamp('2024-03-04 00:00:00'), Timestamp('2024-12-02 00:00:00')]</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.001402378404</v>
+        <v>1.000458458232143</v>
       </c>
     </row>
     <row r="35">
@@ -2211,41 +2271,45 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
+        <v>0.1904761904761904</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.1509433962264151</v>
+      </c>
       <c r="K35" t="n">
-        <v>0.9840255591054312</v>
+        <v>0.9849137931034484</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-04-16 00:00:00'), Timestamp('2022-05-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-04-14 00:00:00'), Timestamp('2022-05-05 00:00:00')]</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0.9987720301766668</v>
+        <v>1.00091165069375</v>
       </c>
     </row>
     <row r="36">
@@ -2261,41 +2325,45 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>29</v>
+      </c>
+      <c r="E36" t="n">
         <v>28</v>
       </c>
-      <c r="E36" t="n">
-        <v>2</v>
-      </c>
       <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.1034482758620689</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12</v>
+      </c>
       <c r="K36" t="n">
-        <v>0.9850984566258648</v>
+        <v>0.9859762675296656</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2024-03-08 00:00:00')]</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2024-03-04 00:00:00')]</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.000458458232143</v>
+        <v>1.000643676596552</v>
       </c>
     </row>
     <row r="37">
@@ -2311,41 +2379,45 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E37" t="n">
+        <v>28</v>
+      </c>
+      <c r="F37" t="n">
         <v>2</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>5.5</v>
+      </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.1142857142857142</v>
+      </c>
       <c r="K37" t="n">
-        <v>0.989888238424694</v>
+        <v>0.99140708915145</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-02-28 00:00:00'), Timestamp('2026-02-04 00:00:00')]</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-02-21 00:00:00'), Timestamp('2026-01-31 00:00:00')]</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.000007921957895</v>
+        <v>1.001831838905556</v>
       </c>
     </row>
     <row r="38">
@@ -2361,41 +2433,45 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E38" t="n">
+        <v>28</v>
+      </c>
+      <c r="F38" t="n">
         <v>2</v>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>3.5</v>
+      </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0888888888888888</v>
+      </c>
       <c r="K38" t="n">
-        <v>0.9914802981895634</v>
+        <v>0.9908306364617044</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2024-03-08 00:00:00'), Timestamp('2026-02-04 00:00:00')]</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2024-03-05 00:00:00'), Timestamp('2026-01-31 00:00:00')]</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.000151351575</v>
+        <v>1.000187996110526</v>
       </c>
     </row>
     <row r="39">
@@ -2411,41 +2487,45 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
+        <v>0.04</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.048780487804878</v>
+      </c>
       <c r="K39" t="n">
-        <v>0.982969664715274</v>
+        <v>0.991918103448276</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-04-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-04-08 00:00:00')]</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.00066815294375</v>
+        <v>1.000151351575</v>
       </c>
     </row>
     <row r="40">
@@ -2461,14 +2541,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2482,7 +2562,7 @@
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
-        <v>0.9845662586482172</v>
+        <v>0.9865951742627346</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2495,7 +2575,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.000643676596552</v>
+        <v>1.001402378404</v>
       </c>
     </row>
     <row r="41">
@@ -2511,14 +2591,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>19</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2532,7 +2612,7 @@
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
-        <v>0.9898828541001063</v>
+        <v>0.989773950484392</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2545,7 +2625,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.000187996110526</v>
+        <v>1.000007921957895</v>
       </c>
     </row>
     <row r="42">
@@ -2568,7 +2648,7 @@
         <v>43</v>
       </c>
       <c r="E42" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F42" t="n">
         <v>9</v>
@@ -2580,13 +2660,13 @@
         <v>0.2093023255813953</v>
       </c>
       <c r="I42" t="n">
-        <v>0.36</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2647058823529412</v>
+        <v>0.2432432432432432</v>
       </c>
       <c r="K42" t="n">
-        <v>0.9237668161434978</v>
+        <v>0.9230769230769232</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2615,45 +2695,45 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E43" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
         <v>3.5</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2307692307692307</v>
+        <v>0.238095238095238</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="J43" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.196078431372549</v>
       </c>
       <c r="K43" t="n">
-        <v>0.955456570155902</v>
+        <v>0.963882618510158</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-01-28 00:00:00'), Timestamp('2021-02-07 00:00:00'), Timestamp('2021-04-17 00:00:00'), Timestamp('2021-11-13 00:00:00')]</t>
+          <t>[Timestamp('2021-01-28 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-01-25 00:00:00'), Timestamp('2021-02-06 00:00:00'), Timestamp('2021-04-10 00:00:00'), Timestamp('2021-11-10 00:00:00')]</t>
+          <t>[Timestamp('2021-01-23 00:00:00'), Timestamp('2022-05-07 00:00:00')]</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0.9963337848115384</v>
+        <v>0.9893466256571428</v>
       </c>
     </row>
     <row r="44">
@@ -2669,14 +2749,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>21</v>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F44" t="n">
         <v>5</v>
@@ -2688,26 +2768,26 @@
         <v>0.238095238095238</v>
       </c>
       <c r="I44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J44" t="n">
         <v>0.217391304347826</v>
       </c>
-      <c r="J44" t="n">
-        <v>0.2272727272727272</v>
-      </c>
       <c r="K44" t="n">
-        <v>0.9642857142857144</v>
+        <v>0.963882618510158</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-01-28 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
+          <t>[Timestamp('2021-11-13 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-01-23 00:00:00'), Timestamp('2022-05-07 00:00:00')]</t>
+          <t>[Timestamp('2021-11-10 00:00:00'), Timestamp('2022-05-05 00:00:00')]</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0.9893466256571428</v>
+        <v>0.9999430023095236</v>
       </c>
     </row>
     <row r="45">
@@ -2723,45 +2803,45 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E45" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F45" t="n">
         <v>5</v>
       </c>
       <c r="G45" t="n">
-        <v>3.5</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="H45" t="n">
-        <v>0.238095238095238</v>
+        <v>0.1923076923076923</v>
       </c>
       <c r="I45" t="n">
-        <v>0.25</v>
+        <v>0.2272727272727272</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2439024390243902</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>0.9642857142857144</v>
+        <v>0.953020134228188</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-13 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
+          <t>[Timestamp('2021-01-28 00:00:00'), Timestamp('2021-04-17 00:00:00'), Timestamp('2021-11-13 00:00:00')]</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-10 00:00:00'), Timestamp('2022-05-05 00:00:00')]</t>
+          <t>[Timestamp('2021-01-25 00:00:00'), Timestamp('2021-04-10 00:00:00'), Timestamp('2021-11-10 00:00:00')]</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.9999430023095236</v>
+        <v>0.9963337848115384</v>
       </c>
     </row>
     <row r="46">
@@ -2784,7 +2864,7 @@
         <v>16</v>
       </c>
       <c r="E46" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F46" t="n">
         <v>4</v>
@@ -2796,13 +2876,13 @@
         <v>0.25</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1538461538461538</v>
+        <v>0.125</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="K46" t="n">
-        <v>0.9732142857142856</v>
+        <v>0.9729119638826184</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2838,7 +2918,7 @@
         <v>18</v>
       </c>
       <c r="E47" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F47" t="n">
         <v>4</v>
@@ -2850,13 +2930,13 @@
         <v>0.2222222222222222</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1904761904761904</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2051282051282051</v>
+        <v>0.1777777777777777</v>
       </c>
       <c r="K47" t="n">
-        <v>0.9688195991091314</v>
+        <v>0.9685393258426966</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2892,7 +2972,7 @@
         <v>18</v>
       </c>
       <c r="E48" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F48" t="n">
         <v>4</v>
@@ -2904,13 +2984,13 @@
         <v>0.2222222222222222</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1142857142857142</v>
       </c>
       <c r="J48" t="n">
-        <v>0.1739130434782608</v>
+        <v>0.1509433962264151</v>
       </c>
       <c r="K48" t="n">
-        <v>0.9686800894854586</v>
+        <v>0.9683257918552036</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2946,7 +3026,7 @@
         <v>19</v>
       </c>
       <c r="E49" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F49" t="n">
         <v>4</v>
@@ -2958,13 +3038,13 @@
         <v>0.2105263157894736</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.1739130434782608</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="K49" t="n">
-        <v>0.967032967032967</v>
+        <v>0.966740576496674</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3000,7 +3080,7 @@
         <v>24</v>
       </c>
       <c r="E50" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F50" t="n">
         <v>4</v>
@@ -3012,13 +3092,13 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1568627450980392</v>
       </c>
       <c r="K50" t="n">
-        <v>0.9553571428571428</v>
+        <v>0.9548532731376976</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3054,7 +3134,7 @@
         <v>29</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F51" t="n">
         <v>4</v>
@@ -3066,13 +3146,13 @@
         <v>0.1379310344827586</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1904761904761904</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="J51" t="n">
-        <v>0.16</v>
+        <v>0.1403508771929824</v>
       </c>
       <c r="K51" t="n">
-        <v>0.9441964285714286</v>
+        <v>0.9435665914221218</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3108,7 +3188,7 @@
         <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -3120,13 +3200,13 @@
         <v>0.25</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2</v>
+        <v>0.0434782608695652</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.074074074074074</v>
       </c>
       <c r="K52" t="n">
-        <v>0.9983991462113126</v>
+        <v>0.9983844911147012</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3162,29 +3242,29 @@
         <v>7</v>
       </c>
       <c r="E53" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
         <v>0.1428571428571428</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>0.0476190476190476</v>
       </c>
       <c r="J53" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="K53" t="n">
-        <v>0.9967982924226254</v>
+        <v>0.9967689822294022</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00')]</t>
+          <t>[Timestamp('2021-11-19 00:00:00')]</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3209,41 +3289,45 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
+        <v>0.0454545454545454</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.06451612903225799</v>
+      </c>
       <c r="K54" t="n">
-        <v>0.9904102290889718</v>
+        <v>0.9956919763058696</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-03-23 00:00:00')]</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-03-22 00:00:00')]</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.9973030966222224</v>
+        <v>1.000019314366667</v>
       </c>
     </row>
     <row r="55">
@@ -3259,41 +3343,45 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>0.0454545454545454</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.06451612903225799</v>
+      </c>
       <c r="K55" t="n">
-        <v>0.9968</v>
+        <v>0.9956919763058696</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-17 00:00:00')]</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0.9996475615833332</v>
+        <v>0.9999071142555556</v>
       </c>
     </row>
     <row r="56">
@@ -3309,41 +3397,45 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>6</v>
+      </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>0.0434782608695652</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.0588235294117647</v>
+      </c>
       <c r="K56" t="n">
-        <v>0.9952</v>
+        <v>0.9946149703823371</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-17 00:00:00')]</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-11 00:00:00')]</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.000019314366667</v>
+        <v>1.0001259667</v>
       </c>
     </row>
     <row r="57">
@@ -3359,41 +3451,45 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3</v>
+      </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.0555555555555555</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
+        <v>0.05</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.0526315789473684</v>
+      </c>
       <c r="K57" t="n">
-        <v>0.9925333333333334</v>
+        <v>0.9908602150537634</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-17 00:00:00')]</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0.9998951158928574</v>
+        <v>0.9973030966222224</v>
       </c>
     </row>
     <row r="58">
@@ -3409,14 +3505,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -3430,7 +3526,7 @@
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="n">
-        <v>0.9968</v>
+        <v>0.9967741935483873</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3443,7 +3539,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0.9999548872833334</v>
+        <v>0.9996475615833332</v>
       </c>
     </row>
     <row r="59">
@@ -3459,14 +3555,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -3480,7 +3576,7 @@
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
-        <v>0.9941333333333332</v>
+        <v>0.992465016146394</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3493,7 +3589,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0.9999854554545454</v>
+        <v>0.9998951158928574</v>
       </c>
     </row>
     <row r="60">
@@ -3509,14 +3605,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -3530,7 +3626,7 @@
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="n">
-        <v>0.9952</v>
+        <v>0.9967707212055974</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3543,7 +3639,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0.9999071142555556</v>
+        <v>0.9999548872833334</v>
       </c>
     </row>
     <row r="61">
@@ -3559,14 +3655,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>11</v>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -3580,7 +3676,7 @@
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
-        <v>0.9941333333333332</v>
+        <v>0.9940796555435952</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3593,7 +3689,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.0001259667</v>
+        <v>0.9999854554545454</v>
       </c>
     </row>
     <row r="62">
@@ -3609,45 +3705,45 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="D62" t="n">
         <v>96</v>
       </c>
       <c r="E62" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F62" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G62" t="n">
-        <v>2.875</v>
+        <v>4.363636363636363</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1041666666666666</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1694915254237288</v>
+        <v>0.2153846153846154</v>
       </c>
       <c r="K62" t="n">
-        <v>0.9534380075798592</v>
+        <v>0.9552401746724892</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-07-24 00:00:00'), Timestamp('2023-09-09 00:00:00'), Timestamp('2023-11-16 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2022-11-29 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-06-22 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-09-22 00:00:00'), Timestamp('2023-10-17 00:00:00'), Timestamp('2023-11-16 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-14 00:00:00'), Timestamp('2023-04-15 00:00:00'), Timestamp('2023-05-01 00:00:00'), Timestamp('2023-07-02 00:00:00'), Timestamp('2023-07-20 00:00:00'), Timestamp('2023-09-07 00:00:00'), Timestamp('2023-11-13 00:00:00'), Timestamp('2023-12-12 00:00:00')]</t>
+          <t>[Timestamp('2022-11-25 00:00:00'), Timestamp('2023-04-15 00:00:00'), Timestamp('2023-04-27 00:00:00'), Timestamp('2023-06-15 00:00:00'), Timestamp('2023-06-30 00:00:00'), Timestamp('2023-07-12 00:00:00'), Timestamp('2023-09-16 00:00:00'), Timestamp('2023-10-16 00:00:00'), Timestamp('2023-11-13 00:00:00'), Timestamp('2023-12-10 00:00:00'), Timestamp('2024-06-25 00:00:00')]</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.9996538151166666</v>
+        <v>0.9997426095854168</v>
       </c>
     </row>
     <row r="63">
@@ -3663,45 +3759,45 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="E63" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G63" t="n">
-        <v>2.833333333333333</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1232876712328767</v>
+        <v>0.1145833333333333</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1705426356589147</v>
       </c>
       <c r="K63" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9536532170119956</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2023-12-16 00:00:00')]</t>
+          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-07-21 00:00:00'), Timestamp('2023-09-09 00:00:00'), Timestamp('2023-09-22 00:00:00'), Timestamp('2023-11-16 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-08 00:00:00'), Timestamp('2023-04-14 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-07-07 00:00:00'), Timestamp('2023-12-13 00:00:00'), Timestamp('2023-12-15 00:00:00')]</t>
+          <t>[Timestamp('2021-04-14 00:00:00'), Timestamp('2023-04-15 00:00:00'), Timestamp('2023-05-01 00:00:00'), Timestamp('2023-07-02 00:00:00'), Timestamp('2023-07-20 00:00:00'), Timestamp('2023-09-07 00:00:00'), Timestamp('2023-09-17 00:00:00'), Timestamp('2023-11-13 00:00:00'), Timestamp('2023-12-12 00:00:00')]</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0.9982399306945204</v>
+        <v>0.9996538151166666</v>
       </c>
     </row>
     <row r="64">
@@ -3717,45 +3813,45 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G64" t="n">
-        <v>3.75</v>
+        <v>3.714285714285714</v>
       </c>
       <c r="H64" t="n">
-        <v>0.09375</v>
+        <v>0.136986301369863</v>
       </c>
       <c r="I64" t="n">
-        <v>0.391304347826087</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1512605042016807</v>
+        <v>0.18348623853211</v>
       </c>
       <c r="K64" t="n">
-        <v>0.9529220779220779</v>
+        <v>0.9658536585365852</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-05-24 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-10-17 00:00:00'), Timestamp('2023-11-16 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2023-12-16 00:00:00'), Timestamp('2024-01-23 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-04-15 00:00:00'), Timestamp('2023-04-27 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-06-30 00:00:00'), Timestamp('2023-07-12 00:00:00'), Timestamp('2023-10-16 00:00:00'), Timestamp('2023-11-13 00:00:00'), Timestamp('2023-12-10 00:00:00')]</t>
+          <t>[Timestamp('2023-04-14 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-07-07 00:00:00'), Timestamp('2023-12-13 00:00:00'), Timestamp('2023-12-15 00:00:00'), Timestamp('2024-01-16 00:00:00'), Timestamp('2024-06-28 00:00:00')]</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0.9997426095854168</v>
+        <v>0.9982399306945204</v>
       </c>
     </row>
     <row r="65">
@@ -3771,45 +3867,45 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E65" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G65" t="n">
-        <v>4.833333333333333</v>
+        <v>3.875</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0795454545454545</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1261261261261261</v>
+        <v>0.1538461538461538</v>
       </c>
       <c r="K65" t="n">
-        <v>0.9562398703403564</v>
+        <v>0.9591947769314472</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-24 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-09-02 00:00:00'), Timestamp('2023-09-09 00:00:00')]</t>
+          <t>[Timestamp('2021-09-07 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-06-22 00:00:00'), Timestamp('2023-09-09 00:00:00'), Timestamp('2023-09-22 00:00:00'), Timestamp('2024-01-23 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-02 00:00:00'), Timestamp('2023-04-18 00:00:00'), Timestamp('2023-05-18 00:00:00'), Timestamp('2023-07-08 00:00:00'), Timestamp('2023-08-27 00:00:00'), Timestamp('2023-09-07 00:00:00')]</t>
+          <t>[Timestamp('2021-09-06 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-05-12 00:00:00'), Timestamp('2023-06-21 00:00:00'), Timestamp('2023-09-05 00:00:00'), Timestamp('2023-09-16 00:00:00'), Timestamp('2024-01-16 00:00:00'), Timestamp('2024-06-27 00:00:00')]</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0.9996920722704544</v>
+        <v>0.9996229292928572</v>
       </c>
     </row>
     <row r="66">
@@ -3825,45 +3921,45 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E66" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G66" t="n">
-        <v>3.4</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0543478260869565</v>
+        <v>0.1022727272727272</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2272727272727272</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="J66" t="n">
-        <v>0.087719298245614</v>
+        <v>0.1475409836065573</v>
       </c>
       <c r="K66" t="n">
-        <v>0.953023758099352</v>
+        <v>0.9569951007076756</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-24 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-08-18 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2023-03-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-06-22 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-09-01 00:00:00'), Timestamp('2023-09-09 00:00:00')]</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-04-15 00:00:00'), Timestamp('2023-05-20 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-08-17 00:00:00'), Timestamp('2023-12-09 00:00:00')]</t>
+          <t>[Timestamp('2023-03-02 00:00:00'), Timestamp('2023-04-18 00:00:00'), Timestamp('2023-05-18 00:00:00'), Timestamp('2023-06-20 00:00:00'), Timestamp('2023-07-08 00:00:00'), Timestamp('2023-08-25 00:00:00'), Timestamp('2023-09-07 00:00:00')]</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.000305725406522</v>
+        <v>0.9996920722704544</v>
       </c>
     </row>
     <row r="67">
@@ -3886,34 +3982,34 @@
         <v>109</v>
       </c>
       <c r="E67" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G67" t="n">
-        <v>4.75</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0458715596330275</v>
+        <v>0.06422018348623849</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.21875</v>
       </c>
       <c r="J67" t="n">
-        <v>0.075187969924812</v>
+        <v>0.09929078014184391</v>
       </c>
       <c r="K67" t="n">
-        <v>0.9438747976254722</v>
+        <v>0.9445350734094616</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-07-03 00:00:00'), Timestamp('2023-09-02 00:00:00'), Timestamp('2023-10-17 00:00:00'), Timestamp('2024-04-12 00:00:00')]</t>
+          <t>[Timestamp('2023-05-19 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-09-01 00:00:00'), Timestamp('2023-09-22 00:00:00'), Timestamp('2023-10-17 00:00:00'), Timestamp('2024-04-12 00:00:00')]</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-06-29 00:00:00'), Timestamp('2023-08-27 00:00:00'), Timestamp('2023-10-11 00:00:00'), Timestamp('2024-04-09 00:00:00')]</t>
+          <t>[Timestamp('2023-05-16 00:00:00'), Timestamp('2023-06-29 00:00:00'), Timestamp('2023-08-27 00:00:00'), Timestamp('2023-09-15 00:00:00'), Timestamp('2023-10-11 00:00:00'), Timestamp('2024-04-09 00:00:00')]</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -3933,45 +4029,45 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E68" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G68" t="n">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0476190476190476</v>
+        <v>0.0697674418604651</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1714285714285714</v>
       </c>
       <c r="J68" t="n">
-        <v>0.0754716981132075</v>
+        <v>0.0991735537190082</v>
       </c>
       <c r="K68" t="n">
-        <v>0.9568500539374326</v>
+        <v>0.9565453557848996</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-07 00:00:00'), Timestamp('2021-09-09 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-09-09 00:00:00')]</t>
+          <t>[Timestamp('2022-11-29 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-06-22 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-06 00:00:00'), Timestamp('2021-09-08 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-09-05 00:00:00')]</t>
+          <t>[Timestamp('2022-11-22 00:00:00'), Timestamp('2023-05-13 00:00:00'), Timestamp('2023-06-15 00:00:00'), Timestamp('2024-06-29 00:00:00')]</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0.9996229292928572</v>
+        <v>0.9991636979720928</v>
       </c>
     </row>
     <row r="69">
@@ -3987,45 +4083,45 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="E69" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F69" t="n">
+        <v>6</v>
+      </c>
+      <c r="G69" t="n">
         <v>3</v>
       </c>
-      <c r="G69" t="n">
-        <v>6.5</v>
-      </c>
       <c r="H69" t="n">
-        <v>0.0394736842105263</v>
+        <v>0.0652173913043478</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1363636363636363</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0612244897959183</v>
+        <v>0.09523809523809521</v>
       </c>
       <c r="K69" t="n">
-        <v>0.960752688172043</v>
+        <v>0.9532354540511148</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-07-03 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-24 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-08-18 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-06-26 00:00:00'), Timestamp('2023-12-08 00:00:00')]</t>
+          <t>[Timestamp('2023-04-15 00:00:00'), Timestamp('2023-05-20 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-08-17 00:00:00'), Timestamp('2023-12-09 00:00:00'), Timestamp('2024-06-30 00:00:00')]</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0.9993811169157892</v>
+        <v>1.000305725406522</v>
       </c>
     </row>
     <row r="70">
@@ -4041,45 +4137,45 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E70" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>4.5</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="H70" t="n">
-        <v>0.024390243902439</v>
+        <v>0.0526315789473684</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.0727272727272727</v>
       </c>
       <c r="K70" t="n">
-        <v>0.9569197630586967</v>
+        <v>0.961060032449973</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-05-24 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2023-07-03 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-05-18 00:00:00'), Timestamp('2023-12-11 00:00:00')]</t>
+          <t>[Timestamp('2023-06-26 00:00:00'), Timestamp('2023-12-08 00:00:00'), Timestamp('2024-06-28 00:00:00')]</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.9996411716707316</v>
+        <v>0.9993811169157892</v>
       </c>
     </row>
     <row r="71">
@@ -4095,41 +4191,45 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E71" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G71" t="n">
+        <v>4.333333333333333</v>
+      </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>0.048780487804878</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="inlineStr"/>
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.0689655172413793</v>
+      </c>
       <c r="K71" t="n">
-        <v>0.9537385691231846</v>
+        <v>0.9576776994031472</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-11-29 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-11-24 00:00:00'), Timestamp('2023-05-14 00:00:00'), Timestamp('2023-12-11 00:00:00')]</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0.9991636979720928</v>
+        <v>0.9996411716707316</v>
       </c>
     </row>
     <row r="72">
@@ -4152,34 +4252,34 @@
         <v>8</v>
       </c>
       <c r="E72" t="n">
+        <v>32</v>
+      </c>
+      <c r="F72" t="n">
         <v>3</v>
       </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
       <c r="G72" t="n">
-        <v>7</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="H72" t="n">
-        <v>0.125</v>
+        <v>0.375</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.09375</v>
       </c>
       <c r="J72" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.15</v>
       </c>
       <c r="K72" t="n">
-        <v>0.996268656716418</v>
+        <v>0.9972914409534128</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2021-06-26 00:00:00'), Timestamp('2021-11-27 00:00:00'), Timestamp('2023-03-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-04 00:00:00')]</t>
+          <t>[Timestamp('2021-06-22 00:00:00'), Timestamp('2021-11-22 00:00:00'), Timestamp('2023-03-04 00:00:00')]</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -4199,14 +4299,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
@@ -4215,29 +4315,29 @@
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.032258064516129</v>
       </c>
       <c r="J73" t="n">
-        <v>0.1538461538461538</v>
+        <v>0.0555555555555555</v>
       </c>
       <c r="K73" t="n">
-        <v>0.995205114544486</v>
+        <v>0.997835497835498</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-17 00:00:00')]</t>
+          <t>[Timestamp('2021-06-18 00:00:00')]</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-16 00:00:00')]</t>
+          <t>[Timestamp('2021-06-17 00:00:00')]</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0.9996626117</v>
+        <v>1.00009744878</v>
       </c>
     </row>
     <row r="74">
@@ -4253,45 +4353,45 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>0.032258064516129</v>
       </c>
       <c r="J74" t="n">
-        <v>0.125</v>
+        <v>0.0526315789473684</v>
       </c>
       <c r="K74" t="n">
-        <v>0.9930777422790202</v>
+        <v>0.9967532467532468</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2021-12-02 00:00:00')]</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-10 00:00:00')]</t>
+          <t>[Timestamp('2021-11-30 00:00:00')]</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0.9989193630571428</v>
+        <v>0.9999668027142856</v>
       </c>
     </row>
     <row r="75">
@@ -4307,41 +4407,45 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="inlineStr"/>
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.0555555555555555</v>
+      </c>
       <c r="K75" t="n">
-        <v>0.9957378795950984</v>
+        <v>0.9951377633711508</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-06-26 00:00:00')]</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-06-21 00:00:00')]</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.9999389337625</v>
+        <v>0.9996626117</v>
       </c>
     </row>
     <row r="76">
@@ -4357,41 +4461,45 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E76" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="inlineStr"/>
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.05</v>
+      </c>
       <c r="K76" t="n">
-        <v>0.9978689397975492</v>
+        <v>0.9929805615550756</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-10 00:00:00')]</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1.00011959195</v>
+        <v>0.9989193630571428</v>
       </c>
     </row>
     <row r="77">
@@ -4407,14 +4515,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>8</v>
       </c>
       <c r="E77" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -4428,7 +4536,7 @@
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="n">
-        <v>0.9957378795950984</v>
+        <v>0.995673336938886</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4441,7 +4549,7 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1.000035119</v>
+        <v>0.9999389337625</v>
       </c>
     </row>
     <row r="78">
@@ -4457,14 +4565,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -4478,7 +4586,7 @@
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="n">
-        <v>0.9973361747469366</v>
+        <v>0.997836668469443</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4491,7 +4599,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.99994125302</v>
+        <v>1.00011959195</v>
       </c>
     </row>
     <row r="79">
@@ -4507,14 +4615,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -4528,7 +4636,7 @@
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
-        <v>0.9973361747469366</v>
+        <v>0.995673336938886</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4541,7 +4649,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1.00009744878</v>
+        <v>1.000035119</v>
       </c>
     </row>
     <row r="80">
@@ -4557,14 +4665,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -4578,7 +4686,7 @@
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="n">
-        <v>0.9962706446457112</v>
+        <v>0.9972958355868036</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4591,7 +4699,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.9999668027142856</v>
+        <v>0.99994125302</v>
       </c>
     </row>
     <row r="81">
@@ -4614,7 +4722,7 @@
         <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -4628,7 +4736,7 @@
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="n">
-        <v>0.998401704848162</v>
+        <v>0.9983775013520824</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4657,45 +4765,45 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
+        <v>28</v>
+      </c>
+      <c r="F82" t="n">
         <v>2</v>
       </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="J82" t="n">
-        <v>0.25</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="K82" t="n">
-        <v>0.9973361747469366</v>
+        <v>0.9994600431965442</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2021-04-11 00:00:00'), Timestamp('2022-11-10 00:00:00')]</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-09 00:00:00')]</t>
+          <t>[Timestamp('2021-04-05 00:00:00'), Timestamp('2022-11-08 00:00:00')]</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>1.00025708725</v>
+        <v>1.0002167471</v>
       </c>
     </row>
     <row r="83">
@@ -4711,45 +4819,45 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.25</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="J83" t="n">
-        <v>0.1538461538461538</v>
+        <v>0.06451612903225799</v>
       </c>
       <c r="K83" t="n">
-        <v>0.9946780202235233</v>
+        <v>0.9983810037776578</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2022-05-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-10 00:00:00')]</t>
+          <t>[Timestamp('2022-05-05 00:00:00')]</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1.000999742136364</v>
+        <v>0.999870388775</v>
       </c>
     </row>
     <row r="84">
@@ -4765,41 +4873,45 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="inlineStr"/>
+        <v>0.0454545454545454</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.0714285714285714</v>
+      </c>
       <c r="K84" t="n">
-        <v>0.9978700745473909</v>
+        <v>0.9973016729627632</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-10 00:00:00')]</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-09 00:00:00')]</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.000021692975</v>
+        <v>1.00025708725</v>
       </c>
     </row>
     <row r="85">
@@ -4815,41 +4927,45 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="inlineStr"/>
+        <v>0.0526315789473684</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.0666666666666666</v>
+      </c>
       <c r="K85" t="n">
-        <v>0.9984025559105432</v>
+        <v>0.9946207638515332</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-11-10 00:00:00')]</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-11-09 00:00:00')]</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1.0002167471</v>
+        <v>1.000999742136364</v>
       </c>
     </row>
     <row r="86">
@@ -4865,14 +4981,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -4886,7 +5002,7 @@
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="n">
-        <v>0.9952076677316294</v>
+        <v>0.9978425026968716</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4899,7 +5015,7 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0.9999991304888888</v>
+        <v>1.000021692975</v>
       </c>
     </row>
     <row r="87">
@@ -4915,14 +5031,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -4936,7 +5052,7 @@
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="n">
-        <v>0.9973375931842384</v>
+        <v>0.9951456310679612</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4949,7 +5065,7 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1.00030686766</v>
+        <v>0.9999991304888888</v>
       </c>
     </row>
     <row r="88">
@@ -4965,14 +5081,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -4986,7 +5102,7 @@
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="n">
-        <v>0.9978700745473909</v>
+        <v>0.9973031283710896</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -4999,7 +5115,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0.999870388775</v>
+        <v>1.00030686766</v>
       </c>
     </row>
     <row r="89">
@@ -5022,7 +5138,7 @@
         <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -5036,7 +5152,7 @@
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="n">
-        <v>0.9984025559105432</v>
+        <v>0.9983818770226536</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5072,7 +5188,7 @@
         <v>9</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -5086,7 +5202,7 @@
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="n">
-        <v>0.9952076677316294</v>
+        <v>0.9951456310679612</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5122,7 +5238,7 @@
         <v>5</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -5136,7 +5252,7 @@
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
-        <v>0.9973375931842384</v>
+        <v>0.9973031283710896</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5172,34 +5288,34 @@
         <v>24</v>
       </c>
       <c r="E92" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G92" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H92" t="n">
-        <v>0.25</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J92" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3111111111111111</v>
       </c>
       <c r="K92" t="n">
-        <v>0.9596412556053812</v>
+        <v>0.9613636363636364</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-01-28 00:00:00'), Timestamp('2021-04-17 00:00:00'), Timestamp('2021-05-20 00:00:00'), Timestamp('2021-11-30 00:00:00')]</t>
+          <t>[Timestamp('2021-01-28 00:00:00'), Timestamp('2021-04-17 00:00:00'), Timestamp('2021-05-20 00:00:00'), Timestamp('2021-11-30 00:00:00'), Timestamp('2021-12-21 00:00:00')]</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-01-25 00:00:00'), Timestamp('2021-04-12 00:00:00'), Timestamp('2021-05-17 00:00:00'), Timestamp('2021-11-27 00:00:00')]</t>
+          <t>[Timestamp('2021-01-25 00:00:00'), Timestamp('2021-04-12 00:00:00'), Timestamp('2021-05-17 00:00:00'), Timestamp('2021-11-27 00:00:00'), Timestamp('2021-12-20 00:00:00')]</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -5219,45 +5335,45 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D93" t="n">
         <v>24</v>
       </c>
       <c r="E93" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F93" t="n">
         <v>6</v>
       </c>
       <c r="G93" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="H93" t="n">
         <v>0.25</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.24</v>
       </c>
       <c r="J93" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2448979591836734</v>
       </c>
       <c r="K93" t="n">
-        <v>0.9596412556053812</v>
+        <v>0.9591836734693876</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-01-28 00:00:00'), Timestamp('2021-04-17 00:00:00'), Timestamp('2021-05-20 00:00:00'), Timestamp('2021-11-30 00:00:00')]</t>
+          <t>[Timestamp('2021-01-28 00:00:00'), Timestamp('2021-05-20 00:00:00'), Timestamp('2021-12-21 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-01-24 00:00:00'), Timestamp('2021-04-12 00:00:00'), Timestamp('2021-05-13 00:00:00'), Timestamp('2021-11-26 00:00:00')]</t>
+          <t>[Timestamp('2021-01-25 00:00:00'), Timestamp('2021-05-18 00:00:00'), Timestamp('2021-12-14 00:00:00'), Timestamp('2022-05-07 00:00:00')]</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.001799184229167</v>
+        <v>1.000553324320833</v>
       </c>
     </row>
     <row r="94">
@@ -5273,45 +5389,45 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E94" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F94" t="n">
+        <v>6</v>
+      </c>
+      <c r="G94" t="n">
         <v>5</v>
       </c>
-      <c r="G94" t="n">
-        <v>2.5</v>
-      </c>
       <c r="H94" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.25</v>
       </c>
       <c r="I94" t="n">
-        <v>0.217391304347826</v>
+        <v>0.25</v>
       </c>
       <c r="J94" t="n">
-        <v>0.2777777777777777</v>
+        <v>0.25</v>
       </c>
       <c r="K94" t="n">
-        <v>0.9823008849557522</v>
+        <v>0.9591836734693876</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-13 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
+          <t>[Timestamp('2021-01-28 00:00:00'), Timestamp('2021-04-17 00:00:00'), Timestamp('2021-05-20 00:00:00'), Timestamp('2021-11-30 00:00:00')]</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-10 00:00:00'), Timestamp('2022-05-07 00:00:00')]</t>
+          <t>[Timestamp('2021-01-24 00:00:00'), Timestamp('2021-04-12 00:00:00'), Timestamp('2021-05-13 00:00:00'), Timestamp('2021-11-26 00:00:00')]</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0.9782552679461538</v>
+        <v>1.001799184229167</v>
       </c>
     </row>
     <row r="95">
@@ -5327,45 +5443,45 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E95" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G95" t="n">
-        <v>2.333333333333333</v>
+        <v>2.5</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.1724137931034483</v>
       </c>
       <c r="J95" t="n">
-        <v>0.1951219512195121</v>
+        <v>0.238095238095238</v>
       </c>
       <c r="K95" t="n">
-        <v>0.9553571428571428</v>
+        <v>0.9821428571428572</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-01-28 00:00:00'), Timestamp('2021-05-20 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
+          <t>[Timestamp('2021-11-13 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-01-25 00:00:00'), Timestamp('2021-05-18 00:00:00'), Timestamp('2022-05-07 00:00:00')]</t>
+          <t>[Timestamp('2021-11-10 00:00:00'), Timestamp('2022-05-07 00:00:00')]</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.000553324320833</v>
+        <v>0.9782552679461538</v>
       </c>
     </row>
     <row r="96">
@@ -5388,34 +5504,34 @@
         <v>20</v>
       </c>
       <c r="E96" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="n">
-        <v>4</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="H96" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1153846153846153</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="J96" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.1568627450980392</v>
       </c>
       <c r="K96" t="n">
-        <v>0.9620535714285714</v>
+        <v>0.9638009049773756</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-13 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
+          <t>[Timestamp('2021-11-13 00:00:00'), Timestamp('2022-03-04 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-09 00:00:00'), Timestamp('2022-05-05 00:00:00')]</t>
+          <t>[Timestamp('2021-11-09 00:00:00'), Timestamp('2022-03-01 00:00:00'), Timestamp('2022-05-05 00:00:00')]</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -5442,7 +5558,7 @@
         <v>16</v>
       </c>
       <c r="E97" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F97" t="n">
         <v>2</v>
@@ -5454,13 +5570,13 @@
         <v>0.125</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1538461538461538</v>
+        <v>0.1</v>
       </c>
       <c r="J97" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="K97" t="n">
-        <v>0.9690265486725664</v>
+        <v>0.9686800894854586</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5496,7 +5612,7 @@
         <v>18</v>
       </c>
       <c r="E98" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F98" t="n">
         <v>2</v>
@@ -5508,13 +5624,13 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="I98" t="n">
-        <v>0.09523809523809521</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="J98" t="n">
-        <v>0.1025641025641025</v>
+        <v>0.0869565217391304</v>
       </c>
       <c r="K98" t="n">
-        <v>0.9644444444444444</v>
+        <v>0.9640449438202248</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5550,7 +5666,7 @@
         <v>18</v>
       </c>
       <c r="E99" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F99" t="n">
         <v>2</v>
@@ -5562,13 +5678,13 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="I99" t="n">
-        <v>0.09523809523809521</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="J99" t="n">
-        <v>0.1025641025641025</v>
+        <v>0.0869565217391304</v>
       </c>
       <c r="K99" t="n">
-        <v>0.9643652561247216</v>
+        <v>0.963963963963964</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5604,7 +5720,7 @@
         <v>24</v>
       </c>
       <c r="E100" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F100" t="n">
         <v>2</v>
@@ -5616,13 +5732,13 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.06451612903225799</v>
       </c>
       <c r="J100" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.0727272727272727</v>
       </c>
       <c r="K100" t="n">
-        <v>0.9510022271714922</v>
+        <v>0.9504504504504504</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5658,34 +5774,34 @@
         <v>24</v>
       </c>
       <c r="E101" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G101" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0416666666666666</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.1</v>
       </c>
       <c r="J101" t="n">
-        <v>0.0512820512820512</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="K101" t="n">
-        <v>0.9492273730684326</v>
+        <v>0.9507829977628636</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-17 00:00:00')]</t>
+          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2022-03-04 00:00:00')]</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-14 00:00:00')]</t>
+          <t>[Timestamp('2021-04-14 00:00:00'), Timestamp('2022-02-26 00:00:00')]</t>
         </is>
       </c>
       <c r="N101" t="n">
@@ -5705,45 +5821,45 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E102" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G102" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H102" t="n">
-        <v>0.125</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2</v>
+        <v>0.2105263157894736</v>
       </c>
       <c r="J102" t="n">
-        <v>0.1538461538461538</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="K102" t="n">
-        <v>0.9962039045553144</v>
+        <v>0.993969298245614</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00')]</t>
+          <t>[Timestamp('2021-03-20 00:00:00'), Timestamp('2021-11-10 00:00:00'), Timestamp('2021-11-19 00:00:00'), Timestamp('2021-12-17 00:00:00')]</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-20 00:00:00')]</t>
+          <t>[Timestamp('2021-03-18 00:00:00'), Timestamp('2021-11-09 00:00:00'), Timestamp('2021-11-14 00:00:00'), Timestamp('2021-12-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1.00087203505</v>
+        <v>1.00015685526</v>
       </c>
     </row>
     <row r="103">
@@ -5759,45 +5875,45 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="D103" t="n">
         <v>15</v>
       </c>
       <c r="E103" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2</v>
+        <v>0.09523809523809521</v>
       </c>
       <c r="J103" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="K103" t="n">
-        <v>0.9924078091106292</v>
+        <v>0.9928806133625412</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-10 00:00:00')]</t>
+          <t>[Timestamp('2021-11-19 00:00:00')]</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-09 00:00:00')]</t>
+          <t>[Timestamp('2021-11-12 00:00:00')]</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>1.00015685526</v>
+        <v>1.000423166673333</v>
       </c>
     </row>
     <row r="104">
@@ -5813,45 +5929,45 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E104" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.125</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="J104" t="n">
-        <v>0.1</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="K104" t="n">
-        <v>0.9924078091106292</v>
+        <v>0.9961706783369804</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00')]</t>
+          <t>[Timestamp('2021-12-23 00:00:00')]</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-17 00:00:00')]</t>
+          <t>[Timestamp('2021-12-22 00:00:00')]</t>
         </is>
       </c>
       <c r="N104" t="n">
-        <v>1.000423166673333</v>
+        <v>1.00087203505</v>
       </c>
     </row>
     <row r="105">
@@ -5867,45 +5983,45 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E105" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0588235294117647</v>
+        <v>0.0625</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2</v>
+        <v>0.0454545454545454</v>
       </c>
       <c r="J105" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.0526315789473684</v>
       </c>
       <c r="K105" t="n">
-        <v>0.9913232104121475</v>
+        <v>0.9917898193760264</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00')]</t>
+          <t>[Timestamp('2021-03-20 00:00:00')]</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-16 00:00:00')]</t>
+          <t>[Timestamp('2021-03-18 00:00:00')]</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0.9999003250411764</v>
+        <v>1.0003872139</v>
       </c>
     </row>
     <row r="106">
@@ -5921,36 +6037,36 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E106" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0555555555555555</v>
+        <v>0.0588235294117647</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2</v>
+        <v>0.0476190476190476</v>
       </c>
       <c r="J106" t="n">
-        <v>0.0869565217391304</v>
+        <v>0.0526315789473684</v>
       </c>
       <c r="K106" t="n">
-        <v>0.9907809110629068</v>
+        <v>0.9912424740010948</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00')]</t>
+          <t>[Timestamp('2021-11-19 00:00:00')]</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -5959,7 +6075,7 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>1.000087259683333</v>
+        <v>0.9999003250411764</v>
       </c>
     </row>
     <row r="107">
@@ -5975,45 +6091,45 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E107" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0526315789473684</v>
+        <v>0.0555555555555555</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2</v>
+        <v>0.0476190476190476</v>
       </c>
       <c r="J107" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.0512820512820512</v>
       </c>
       <c r="K107" t="n">
-        <v>0.990238611713666</v>
+        <v>0.9906951286261632</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2021-11-19 00:00:00')]</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-10 00:00:00')]</t>
+          <t>[Timestamp('2021-11-16 00:00:00')]</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0.9999901278157894</v>
+        <v>1.000087259683333</v>
       </c>
     </row>
     <row r="108">
@@ -6029,41 +6145,45 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D108" t="n">
+        <v>19</v>
+      </c>
+      <c r="E108" t="n">
         <v>23</v>
       </c>
-      <c r="E108" t="n">
-        <v>5</v>
-      </c>
       <c r="F108" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>0.0526315789473684</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" t="inlineStr"/>
+        <v>0.0454545454545454</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.048780487804878</v>
+      </c>
       <c r="K108" t="n">
-        <v>0.9875473741201948</v>
+        <v>0.9901477832512317</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-10 00:00:00')]</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>0.9978440998130436</v>
+        <v>0.9999901278157894</v>
       </c>
     </row>
     <row r="109">
@@ -6079,41 +6199,45 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E109" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>0.0434782608695652</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="inlineStr"/>
+        <v>0.0555555555555555</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.048780487804878</v>
+      </c>
       <c r="K109" t="n">
-        <v>0.9924119241192412</v>
+        <v>0.98798470780994</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-17 00:00:00')]</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0.9997379059571428</v>
+        <v>0.9978440998130436</v>
       </c>
     </row>
     <row r="110">
@@ -6129,14 +6253,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E110" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -6150,7 +6274,7 @@
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
-        <v>0.9897018970189702</v>
+        <v>0.9923497267759562</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6163,7 +6287,7 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0.9999319296473684</v>
+        <v>0.9997379059571428</v>
       </c>
     </row>
     <row r="111">
@@ -6179,14 +6303,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E111" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -6200,7 +6324,7 @@
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="n">
-        <v>0.9913279132791328</v>
+        <v>0.9896061269146608</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6213,7 +6337,7 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1.0003872139</v>
+        <v>0.9999319296473684</v>
       </c>
     </row>
     <row r="112">
@@ -6236,34 +6360,34 @@
         <v>86</v>
       </c>
       <c r="E112" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F112" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G112" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1162790697674418</v>
+        <v>0.127906976744186</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3571428571428571</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="J112" t="n">
-        <v>0.1754385964912281</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="K112" t="n">
-        <v>0.9583561643835616</v>
+        <v>0.9586549062844544</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2023-12-16 00:00:00')]</t>
+          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2023-12-16 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-08 00:00:00'), Timestamp('2023-04-14 00:00:00'), Timestamp('2023-07-10 00:00:00'), Timestamp('2023-12-13 00:00:00'), Timestamp('2023-12-15 00:00:00')]</t>
+          <t>[Timestamp('2023-04-14 00:00:00'), Timestamp('2023-07-10 00:00:00'), Timestamp('2023-12-13 00:00:00'), Timestamp('2023-12-15 00:00:00'), Timestamp('2024-06-28 00:00:00')]</t>
         </is>
       </c>
       <c r="N112" t="n">
@@ -6290,34 +6414,34 @@
         <v>94</v>
       </c>
       <c r="E113" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F113" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G113" t="n">
-        <v>2.571428571428572</v>
+        <v>3.111111111111111</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0851063829787234</v>
+        <v>0.1063829787234042</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="J113" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.1574803149606299</v>
       </c>
       <c r="K113" t="n">
-        <v>0.9527991218441272</v>
+        <v>0.9535398230088497</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2021-09-07 00:00:00'), Timestamp('2023-03-09 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-11-16 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2021-09-07 00:00:00'), Timestamp('2023-03-09 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-09-22 00:00:00'), Timestamp('2023-11-16 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-13 00:00:00'), Timestamp('2021-09-06 00:00:00'), Timestamp('2023-03-07 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-07-11 00:00:00'), Timestamp('2023-11-10 00:00:00'), Timestamp('2023-12-13 00:00:00')]</t>
+          <t>[Timestamp('2021-04-13 00:00:00'), Timestamp('2021-09-06 00:00:00'), Timestamp('2023-03-07 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-07-11 00:00:00'), Timestamp('2023-09-15 00:00:00'), Timestamp('2023-11-10 00:00:00'), Timestamp('2023-12-13 00:00:00'), Timestamp('2024-06-28 00:00:00')]</t>
         </is>
       </c>
       <c r="N113" t="n">
@@ -6337,45 +6461,45 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E114" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F114" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G114" t="n">
-        <v>3.2</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0515463917525773</v>
+        <v>0.0843373493975903</v>
       </c>
       <c r="I114" t="n">
-        <v>0.217391304347826</v>
+        <v>0.2058823529411764</v>
       </c>
       <c r="J114" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.1196581196581196</v>
       </c>
       <c r="K114" t="n">
-        <v>0.9495614035087721</v>
+        <v>0.9579878385848536</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-07 00:00:00'), Timestamp('2021-09-09 00:00:00'), Timestamp('2023-05-24 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-09-02 00:00:00')]</t>
+          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-09-01 00:00:00'), Timestamp('2023-09-22 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-06 00:00:00'), Timestamp('2021-09-08 00:00:00'), Timestamp('2023-05-18 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-08-27 00:00:00')]</t>
+          <t>[Timestamp('2023-04-16 00:00:00'), Timestamp('2023-05-14 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-08-27 00:00:00'), Timestamp('2023-09-18 00:00:00'), Timestamp('2023-12-11 00:00:00')]</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>0.9995436067773196</v>
+        <v>0.999525704307229</v>
       </c>
     </row>
     <row r="115">
@@ -6391,45 +6515,45 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E115" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F115" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G115" t="n">
-        <v>5</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0493827160493827</v>
+        <v>0.0777777777777777</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="J115" t="n">
-        <v>0.0776699029126213</v>
+        <v>0.1138211382113821</v>
       </c>
       <c r="K115" t="n">
-        <v>0.9578313253012049</v>
+        <v>0.9540929203539824</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2021-09-07 00:00:00'), Timestamp('2023-03-09 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-09-09 00:00:00'), Timestamp('2023-09-22 00:00:00')]</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-04-14 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-07-07 00:00:00'), Timestamp('2023-12-08 00:00:00')]</t>
+          <t>[Timestamp('2021-09-06 00:00:00'), Timestamp('2023-03-06 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-05-12 00:00:00'), Timestamp('2023-09-05 00:00:00'), Timestamp('2023-09-16 00:00:00')]</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0.9995344067876542</v>
+        <v>0.9995213886199996</v>
       </c>
     </row>
     <row r="116">
@@ -6445,45 +6569,45 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="E116" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F116" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G116" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0481927710843373</v>
+        <v>0.0721649484536082</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="J116" t="n">
-        <v>0.0761904761904762</v>
+        <v>0.109375</v>
       </c>
       <c r="K116" t="n">
-        <v>0.956664838178826</v>
+        <v>0.9503311258278144</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-09-02 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2021-09-07 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-09-01 00:00:00'), Timestamp('2023-09-22 00:00:00')]</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-04-16 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-08-27 00:00:00'), Timestamp('2023-12-11 00:00:00')]</t>
+          <t>[Timestamp('2021-09-06 00:00:00'), Timestamp('2023-05-12 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-08-27 00:00:00'), Timestamp('2023-09-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0.999525704307229</v>
+        <v>0.9995436067773196</v>
       </c>
     </row>
     <row r="117">
@@ -6499,45 +6623,45 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E117" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F117" t="n">
+        <v>6</v>
+      </c>
+      <c r="G117" t="n">
         <v>4</v>
       </c>
-      <c r="G117" t="n">
-        <v>2.25</v>
-      </c>
       <c r="H117" t="n">
-        <v>0.0444444444444444</v>
+        <v>0.0618556701030927</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1904761904761904</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="J117" t="n">
-        <v>0.072072072072072</v>
+        <v>0.0916030534351145</v>
       </c>
       <c r="K117" t="n">
-        <v>0.9528250137136588</v>
+        <v>0.949862258953168</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-07 00:00:00'), Timestamp('2023-03-09 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-09-09 00:00:00')]</t>
+          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-07-19 00:00:00')]</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-06 00:00:00'), Timestamp('2023-03-06 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-09-05 00:00:00')]</t>
+          <t>[Timestamp('2023-04-15 00:00:00'), Timestamp('2023-05-14 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-07-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0.9995213886199996</v>
+        <v>0.9993703609752578</v>
       </c>
     </row>
     <row r="118">
@@ -6553,45 +6677,45 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="E118" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F118" t="n">
         <v>4</v>
       </c>
       <c r="G118" t="n">
-        <v>2.666666666666667</v>
+        <v>5</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0412371134020618</v>
+        <v>0.0493827160493827</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1739130434782608</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="J118" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.06956521739130429</v>
       </c>
       <c r="K118" t="n">
-        <v>0.9490690032858708</v>
+        <v>0.9575991189427312</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-07-03 00:00:00')]</t>
+          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-08 00:00:00'), Timestamp('2023-04-15 00:00:00'), Timestamp('2023-07-01 00:00:00')]</t>
+          <t>[Timestamp('2023-04-14 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-07-07 00:00:00'), Timestamp('2023-12-08 00:00:00')]</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>0.9993703609752578</v>
+        <v>0.9995344067876542</v>
       </c>
     </row>
     <row r="119">
@@ -6614,34 +6738,34 @@
         <v>98</v>
       </c>
       <c r="E119" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F119" t="n">
         <v>4</v>
       </c>
       <c r="G119" t="n">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="H119" t="n">
         <v>0.0408163265306122</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1904761904761904</v>
+        <v>0.125</v>
       </c>
       <c r="J119" t="n">
-        <v>0.0672268907563025</v>
+        <v>0.0615384615384615</v>
       </c>
       <c r="K119" t="n">
-        <v>0.9484931506849316</v>
+        <v>0.948180815876516</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-07-14 00:00:00'), Timestamp('2023-07-24 00:00:00'), Timestamp('2023-10-17 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2023-05-19 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-10-17 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-07-10 00:00:00'), Timestamp('2023-07-21 00:00:00'), Timestamp('2023-10-10 00:00:00'), Timestamp('2023-12-11 00:00:00')]</t>
+          <t>[Timestamp('2023-05-14 00:00:00'), Timestamp('2023-07-10 00:00:00'), Timestamp('2023-10-10 00:00:00'), Timestamp('2023-12-11 00:00:00')]</t>
         </is>
       </c>
       <c r="N119" t="n">
@@ -6668,34 +6792,34 @@
         <v>85</v>
       </c>
       <c r="E120" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>5.5</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0235294117647058</v>
+        <v>0.0352941176470588</v>
       </c>
       <c r="I120" t="n">
         <v>0.0909090909090909</v>
       </c>
       <c r="J120" t="n">
-        <v>0.0373831775700934</v>
+        <v>0.0508474576271186</v>
       </c>
       <c r="K120" t="n">
-        <v>0.9545205479452056</v>
+        <v>0.9547461368653422</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-09-02 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2023-09-01 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-08-27 00:00:00'), Timestamp('2023-12-09 00:00:00')]</t>
+          <t>[Timestamp('2023-08-27 00:00:00'), Timestamp('2023-12-09 00:00:00'), Timestamp('2024-06-25 00:00:00')]</t>
         </is>
       </c>
       <c r="N120" t="n">
@@ -6722,34 +6846,34 @@
         <v>89</v>
       </c>
       <c r="E121" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G121" t="n">
-        <v>3.5</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0224719101123595</v>
+        <v>0.0337078651685393</v>
       </c>
       <c r="I121" t="n">
-        <v>0.0869565217391304</v>
+        <v>0.088235294117647</v>
       </c>
       <c r="J121" t="n">
-        <v>0.0357142857142857</v>
+        <v>0.048780487804878</v>
       </c>
       <c r="K121" t="n">
-        <v>0.9523809523809524</v>
+        <v>0.9525909592061742</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-08-18 00:00:00'), Timestamp('2023-09-02 00:00:00')]</t>
+          <t>[Timestamp('2023-08-18 00:00:00'), Timestamp('2023-09-01 00:00:00'), Timestamp('2023-09-22 00:00:00')]</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-08-17 00:00:00'), Timestamp('2023-08-27 00:00:00')]</t>
+          <t>[Timestamp('2023-08-17 00:00:00'), Timestamp('2023-08-27 00:00:00'), Timestamp('2023-09-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N121" t="n">
@@ -6769,45 +6893,45 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E122" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.1904761904761904</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>0.1379310344827586</v>
       </c>
       <c r="J122" t="n">
-        <v>0.125</v>
+        <v>0.16</v>
       </c>
       <c r="K122" t="n">
-        <v>0.9929691725256896</v>
+        <v>0.9906542056074766</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2021-03-19 00:00:00'), Timestamp('2023-03-20 00:00:00')]</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-10 00:00:00')]</t>
+          <t>[Timestamp('2021-03-18 00:00:00'), Timestamp('2023-03-14 00:00:00')]</t>
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0.9985274186714286</v>
+        <v>1.000390054557143</v>
       </c>
     </row>
     <row r="123">
@@ -6823,41 +6947,45 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E123" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="inlineStr"/>
+        <v>0.032258064516129</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.0512820512820512</v>
+      </c>
       <c r="K123" t="n">
-        <v>0.9886363636363636</v>
+        <v>0.996149614961496</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-06-18 00:00:00')]</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-06-17 00:00:00')]</t>
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1.000390054557143</v>
+        <v>1.00012734935</v>
       </c>
     </row>
     <row r="124">
@@ -6873,41 +7001,45 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2</v>
+      </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" t="inlineStr"/>
+        <v>0.032258064516129</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.0465116279069767</v>
+      </c>
       <c r="K124" t="n">
-        <v>0.9902597402597404</v>
+        <v>0.993949394939494</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-20 00:00:00')]</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-18 00:00:00')]</t>
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0.999677490588889</v>
+        <v>0.9999588059666666</v>
       </c>
     </row>
     <row r="125">
@@ -6930,30 +7062,34 @@
         <v>13</v>
       </c>
       <c r="E125" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G125" t="n">
+        <v>6</v>
+      </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" t="inlineStr"/>
+        <v>0.03125</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.0444444444444444</v>
+      </c>
       <c r="K125" t="n">
-        <v>0.9929615592853276</v>
+        <v>0.9933993399339934</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-11-27 00:00:00')]</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-11-21 00:00:00')]</t>
         </is>
       </c>
       <c r="N125" t="n">
@@ -6973,41 +7109,45 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E126" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="inlineStr"/>
+        <v>0.0384615384615384</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.05</v>
+      </c>
       <c r="K126" t="n">
-        <v>0.995668651867894</v>
+        <v>0.992872807017544</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2023-03-10 00:00:00')]</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0.9999503417875</v>
+        <v>0.9985274186714286</v>
       </c>
     </row>
     <row r="127">
@@ -7023,14 +7163,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E127" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -7044,7 +7184,7 @@
       </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="n">
-        <v>0.9962100703844072</v>
+        <v>0.9901153212520593</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -7057,7 +7197,7 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>0.9999509634857142</v>
+        <v>0.999677490588889</v>
       </c>
     </row>
     <row r="128">
@@ -7073,14 +7213,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E128" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -7094,7 +7234,7 @@
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="n">
-        <v>0.9935029778018408</v>
+        <v>0.9956019791094008</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -7107,7 +7247,7 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>0.9999588059666666</v>
+        <v>0.9999503417875</v>
       </c>
     </row>
     <row r="129">
@@ -7123,14 +7263,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E129" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -7144,7 +7284,7 @@
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="n">
-        <v>0.9929615592853276</v>
+        <v>0.9961517317207256</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -7157,7 +7297,7 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>1.000213376469231</v>
+        <v>0.9999509634857142</v>
       </c>
     </row>
     <row r="130">
@@ -7173,14 +7313,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E130" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -7194,7 +7334,7 @@
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="n">
-        <v>0.9935029778018408</v>
+        <v>0.9928610653487095</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -7207,7 +7347,7 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>1.000072488391666</v>
+        <v>1.000213376469231</v>
       </c>
     </row>
     <row r="131">
@@ -7223,14 +7363,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E131" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -7244,7 +7384,7 @@
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="n">
-        <v>0.995668651867894</v>
+        <v>0.9934029686641012</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -7257,7 +7397,7 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>1.00012734935</v>
+        <v>1.000072488391666</v>
       </c>
     </row>
     <row r="132">
@@ -7273,45 +7413,45 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E132" t="n">
+        <v>28</v>
+      </c>
+      <c r="F132" t="n">
         <v>2</v>
       </c>
-      <c r="F132" t="n">
-        <v>1</v>
-      </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0555555555555555</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="J132" t="n">
-        <v>0.09999999999999989</v>
+        <v>0.0930232558139534</v>
       </c>
       <c r="K132" t="n">
-        <v>0.9908058409951324</v>
+        <v>0.9928649835345774</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2021-04-11 00:00:00'), Timestamp('2022-11-10 00:00:00')]</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-10 00:00:00')]</t>
+          <t>[Timestamp('2021-04-05 00:00:00'), Timestamp('2022-11-08 00:00:00')]</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>1.000793944322222</v>
+        <v>1.0001331638</v>
       </c>
     </row>
     <row r="133">
@@ -7327,41 +7467,45 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G133" t="n">
+        <v>5</v>
+      </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" t="inlineStr"/>
+        <v>0.0357142857142857</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.0555555555555555</v>
+      </c>
       <c r="K133" t="n">
-        <v>0.9940476190476192</v>
+        <v>0.9961601755348328</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-04-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-04-06 00:00:00')]</t>
         </is>
       </c>
       <c r="N133" t="n">
-        <v>1.000500685154546</v>
+        <v>1.0004005344125</v>
       </c>
     </row>
     <row r="134">
@@ -7377,41 +7521,45 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E134" t="n">
+        <v>28</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" t="n">
         <v>2</v>
       </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" t="inlineStr"/>
+        <v>0.037037037037037</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.0526315789473684</v>
+      </c>
       <c r="K134" t="n">
-        <v>0.9918831168831168</v>
+        <v>0.9945145364783324</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-03-19 00:00:00')]</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-03-17 00:00:00')]</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>1.0001331638</v>
+        <v>0.999869571609091</v>
       </c>
     </row>
     <row r="135">
@@ -7434,30 +7582,34 @@
         <v>15</v>
       </c>
       <c r="E135" t="n">
+        <v>28</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="n">
         <v>2</v>
       </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" t="inlineStr"/>
+        <v>0.0454545454545454</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.054054054054054</v>
+      </c>
       <c r="K135" t="n">
-        <v>0.9918831168831168</v>
+        <v>0.9923245614035088</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-11-10 00:00:00')]</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-11-08 00:00:00')]</t>
         </is>
       </c>
       <c r="N135" t="n">
@@ -7477,41 +7629,45 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E136" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>0.0555555555555555</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" t="inlineStr"/>
+        <v>0.0555555555555555</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.0555555555555555</v>
+      </c>
       <c r="K136" t="n">
-        <v>0.9918831168831168</v>
+        <v>0.9907103825136612</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-11-10 00:00:00')]</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-11-09 00:00:00')]</t>
         </is>
       </c>
       <c r="N136" t="n">
-        <v>1.000424328966667</v>
+        <v>1.000793944322222</v>
       </c>
     </row>
     <row r="137">
@@ -7527,14 +7683,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E137" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -7548,7 +7704,7 @@
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="n">
-        <v>0.9956709956709956</v>
+        <v>0.993972602739726</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -7561,7 +7717,7 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>1.0004474541125</v>
+        <v>1.000500685154546</v>
       </c>
     </row>
     <row r="138">
@@ -7577,14 +7733,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D138" t="n">
         <v>15</v>
       </c>
       <c r="E138" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -7598,7 +7754,7 @@
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="n">
-        <v>0.9918831168831168</v>
+        <v>0.9917808219178084</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -7611,7 +7767,7 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>1.000221977633333</v>
+        <v>1.000424328966667</v>
       </c>
     </row>
     <row r="139">
@@ -7627,14 +7783,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E139" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -7648,7 +7804,7 @@
       </c>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="n">
-        <v>0.99512987012987</v>
+        <v>0.9956164383561644</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -7661,7 +7817,7 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>1.000023049333334</v>
+        <v>1.0004474541125</v>
       </c>
     </row>
     <row r="140">
@@ -7677,14 +7833,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E140" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -7698,7 +7854,7 @@
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="n">
-        <v>0.9940476190476192</v>
+        <v>0.9917763157894736</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -7711,7 +7867,7 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>0.999869571609091</v>
+        <v>1.000221977633333</v>
       </c>
     </row>
     <row r="141">
@@ -7727,14 +7883,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E141" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -7748,7 +7904,7 @@
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="n">
-        <v>0.9956709956709956</v>
+        <v>0.9950684931506848</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -7761,7 +7917,7 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>1.0004005344125</v>
+        <v>1.000023049333334</v>
       </c>
     </row>
     <row r="142">
@@ -7777,45 +7933,45 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E142" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F142" t="n">
         <v>6</v>
       </c>
       <c r="G142" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="H142" t="n">
-        <v>0.2142857142857142</v>
+        <v>0.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="J142" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K142" t="n">
-        <v>0.948955916473318</v>
+        <v>0.9549763033175356</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2021-11-13 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
+          <t>[Timestamp('2021-05-20 00:00:00'), Timestamp('2021-11-30 00:00:00'), Timestamp('2021-12-21 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-10 00:00:00'), Timestamp('2021-11-10 00:00:00'), Timestamp('2022-05-07 00:00:00')]</t>
+          <t>[Timestamp('2021-05-18 00:00:00'), Timestamp('2021-11-26 00:00:00'), Timestamp('2021-12-14 00:00:00'), Timestamp('2022-05-07 00:00:00')]</t>
         </is>
       </c>
       <c r="N142" t="n">
-        <v>0.9993290992892856</v>
+        <v>1.000728913668</v>
       </c>
     </row>
     <row r="143">
@@ -7831,45 +7987,45 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E143" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G143" t="n">
-        <v>2.666666666666667</v>
+        <v>4</v>
       </c>
       <c r="H143" t="n">
-        <v>0.2</v>
+        <v>0.2142857142857142</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2272727272727272</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="J143" t="n">
-        <v>0.2127659574468085</v>
+        <v>0.2105263157894736</v>
       </c>
       <c r="K143" t="n">
-        <v>0.9531615925058547</v>
+        <v>0.9485981308411215</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-05-20 00:00:00'), Timestamp('2021-11-30 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
+          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2021-11-13 00:00:00'), Timestamp('2022-05-09 00:00:00')]</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-05-18 00:00:00'), Timestamp('2021-11-26 00:00:00'), Timestamp('2022-05-07 00:00:00')]</t>
+          <t>[Timestamp('2021-04-10 00:00:00'), Timestamp('2021-11-10 00:00:00'), Timestamp('2022-05-07 00:00:00')]</t>
         </is>
       </c>
       <c r="N143" t="n">
-        <v>1.000728913668</v>
+        <v>0.9993290992892856</v>
       </c>
     </row>
     <row r="144">
@@ -7892,7 +8048,7 @@
         <v>14</v>
       </c>
       <c r="E144" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F144" t="n">
         <v>3</v>
@@ -7904,13 +8060,13 @@
         <v>0.2142857142857142</v>
       </c>
       <c r="I144" t="n">
+        <v>0.1153846153846153</v>
+      </c>
+      <c r="J144" t="n">
         <v>0.15</v>
       </c>
-      <c r="J144" t="n">
-        <v>0.1764705882352941</v>
-      </c>
       <c r="K144" t="n">
-        <v>0.97459584295612</v>
+        <v>0.9743589743589745</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -7946,7 +8102,7 @@
         <v>15</v>
       </c>
       <c r="E145" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F145" t="n">
         <v>3</v>
@@ -7958,13 +8114,13 @@
         <v>0.2</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1363636363636363</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="J145" t="n">
-        <v>0.1621621621621621</v>
+        <v>0.1395348837209302</v>
       </c>
       <c r="K145" t="n">
-        <v>0.9725400457665904</v>
+        <v>0.9723502304147466</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -8000,7 +8156,7 @@
         <v>19</v>
       </c>
       <c r="E146" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F146" t="n">
         <v>2</v>
@@ -8012,13 +8168,13 @@
         <v>0.1052631578947368</v>
       </c>
       <c r="I146" t="n">
-        <v>0.08</v>
+        <v>0.06451612903225799</v>
       </c>
       <c r="J146" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.0799999999999999</v>
       </c>
       <c r="K146" t="n">
-        <v>0.9604651162790696</v>
+        <v>0.960093896713615</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -8054,7 +8210,7 @@
         <v>20</v>
       </c>
       <c r="E147" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F147" t="n">
         <v>2</v>
@@ -8066,13 +8222,13 @@
         <v>0.1</v>
       </c>
       <c r="I147" t="n">
-        <v>0.08</v>
+        <v>0.06451612903225799</v>
       </c>
       <c r="J147" t="n">
-        <v>0.0888888888888888</v>
+        <v>0.07843137254901961</v>
       </c>
       <c r="K147" t="n">
-        <v>0.9581395348837209</v>
+        <v>0.9577464788732394</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -8108,7 +8264,7 @@
         <v>24</v>
       </c>
       <c r="E148" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F148" t="n">
         <v>2</v>
@@ -8120,13 +8276,13 @@
         <v>0.0833333333333333</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0606060606060606</v>
       </c>
       <c r="J148" t="n">
-        <v>0.08</v>
+        <v>0.0701754385964912</v>
       </c>
       <c r="K148" t="n">
-        <v>0.948955916473318</v>
+        <v>0.9484777517564404</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -8162,7 +8318,7 @@
         <v>23</v>
       </c>
       <c r="E149" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F149" t="n">
         <v>1</v>
@@ -8174,13 +8330,13 @@
         <v>0.0434782608695652</v>
       </c>
       <c r="I149" t="n">
-        <v>0.05</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="J149" t="n">
-        <v>0.0465116279069767</v>
+        <v>0.0399999999999999</v>
       </c>
       <c r="K149" t="n">
-        <v>0.948955916473318</v>
+        <v>0.9484777517564404</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -8216,7 +8372,7 @@
         <v>24</v>
       </c>
       <c r="E150" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F150" t="n">
         <v>1</v>
@@ -8228,13 +8384,13 @@
         <v>0.0416666666666666</v>
       </c>
       <c r="I150" t="n">
-        <v>0.04</v>
+        <v>0.03125</v>
       </c>
       <c r="J150" t="n">
-        <v>0.0408163265306122</v>
+        <v>0.0357142857142857</v>
       </c>
       <c r="K150" t="n">
-        <v>0.9466357308584686</v>
+        <v>0.9461358313817332</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -8270,7 +8426,7 @@
         <v>24</v>
       </c>
       <c r="E151" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F151" t="n">
         <v>1</v>
@@ -8282,13 +8438,13 @@
         <v>0.0416666666666666</v>
       </c>
       <c r="I151" t="n">
-        <v>0.04</v>
+        <v>0.03125</v>
       </c>
       <c r="J151" t="n">
-        <v>0.0408163265306122</v>
+        <v>0.0357142857142857</v>
       </c>
       <c r="K151" t="n">
-        <v>0.9466357308584686</v>
+        <v>0.9461358313817332</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -8317,45 +8473,45 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E152" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G152" t="n">
         <v>4</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1875</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="J152" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="K152" t="n">
-        <v>0.9928295642581356</v>
+        <v>0.9927737632017788</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00'), Timestamp('2021-12-06 00:00:00')]</t>
+          <t>[Timestamp('2021-11-19 00:00:00'), Timestamp('2021-12-23 00:00:00')]</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-17 00:00:00'), Timestamp('2021-12-04 00:00:00')]</t>
+          <t>[Timestamp('2021-11-12 00:00:00'), Timestamp('2021-12-22 00:00:00')]</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1.0005252102</v>
+        <v>1.00070149929375</v>
       </c>
     </row>
     <row r="153">
@@ -8371,45 +8527,45 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E153" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G153" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H153" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1363636363636363</v>
       </c>
       <c r="J153" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="K153" t="n">
-        <v>0.9922779922779924</v>
+        <v>0.9905555555555556</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00')]</t>
+          <t>[Timestamp('2021-11-19 00:00:00'), Timestamp('2023-03-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-17 00:00:00')]</t>
+          <t>[Timestamp('2021-11-12 00:00:00'), Timestamp('2023-03-10 00:00:00')]</t>
         </is>
       </c>
       <c r="N153" t="n">
-        <v>1.00070149929375</v>
+        <v>1.000146235015</v>
       </c>
     </row>
     <row r="154">
@@ -8425,45 +8581,45 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E154" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G154" t="n">
-        <v>7</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0588235294117647</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2</v>
+        <v>0.1363636363636363</v>
       </c>
       <c r="J154" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.1395348837209302</v>
       </c>
       <c r="K154" t="n">
-        <v>0.9911797133406836</v>
+        <v>0.9899888765294772</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00')]</t>
+          <t>[Timestamp('2021-03-26 00:00:00'), Timestamp('2021-12-06 00:00:00'), Timestamp('2021-12-17 00:00:00')]</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-16 00:00:00')]</t>
+          <t>[Timestamp('2021-03-24 00:00:00'), Timestamp('2021-11-30 00:00:00'), Timestamp('2021-12-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N154" t="n">
-        <v>0.9995186151588232</v>
+        <v>0.9999717084809524</v>
       </c>
     </row>
     <row r="155">
@@ -8479,45 +8635,45 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E155" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G155" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="H155" t="n">
-        <v>0.05</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="J155" t="n">
-        <v>0.08</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="K155" t="n">
-        <v>0.9895259095920618</v>
+        <v>0.9899888765294772</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2021-11-19 00:00:00'), Timestamp('2021-12-17 00:00:00')]</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-10 00:00:00')]</t>
+          <t>[Timestamp('2021-11-14 00:00:00'), Timestamp('2021-12-15 00:00:00')]</t>
         </is>
       </c>
       <c r="N155" t="n">
-        <v>1.000146235015</v>
+        <v>1.000002888842857</v>
       </c>
     </row>
     <row r="156">
@@ -8533,45 +8689,45 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E156" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G156" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H156" t="n">
-        <v>0.0476190476190476</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J156" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="K156" t="n">
-        <v>0.9889746416758544</v>
+        <v>0.9927737632017788</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-12-06 00:00:00')]</t>
+          <t>[Timestamp('2021-11-19 00:00:00'), Timestamp('2021-12-06 00:00:00')]</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-30 00:00:00')]</t>
+          <t>[Timestamp('2021-11-17 00:00:00'), Timestamp('2021-12-04 00:00:00')]</t>
         </is>
       </c>
       <c r="N156" t="n">
-        <v>0.9999717084809524</v>
+        <v>1.0005252102</v>
       </c>
     </row>
     <row r="157">
@@ -8587,45 +8743,45 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E157" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G157" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H157" t="n">
-        <v>0.0476190476190476</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2</v>
+        <v>0.09523809523809521</v>
       </c>
       <c r="J157" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="K157" t="n">
-        <v>0.9889746416758544</v>
+        <v>0.9916620344635908</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00')]</t>
+          <t>[Timestamp('2021-04-08 00:00:00'), Timestamp('2021-11-19 00:00:00')]</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-16 00:00:00')]</t>
+          <t>[Timestamp('2021-04-05 00:00:00'), Timestamp('2021-11-16 00:00:00')]</t>
         </is>
       </c>
       <c r="N157" t="n">
-        <v>1.000002888842857</v>
+        <v>0.9995186151588232</v>
       </c>
     </row>
     <row r="158">
@@ -8641,45 +8797,45 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D158" t="n">
         <v>23</v>
       </c>
       <c r="E158" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G158" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H158" t="n">
-        <v>0.0434782608695652</v>
+        <v>0.0869565217391304</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2</v>
+        <v>0.09523809523809521</v>
       </c>
       <c r="J158" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="K158" t="n">
-        <v>0.98787210584344</v>
+        <v>0.98834628190899</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-23 00:00:00')]</t>
+          <t>[Timestamp('2021-12-17 00:00:00')]</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-11-16 00:00:00')]</t>
+          <t>[Timestamp('2021-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="N158" t="n">
-        <v>1.000022093113044</v>
+        <v>0.9977495565739132</v>
       </c>
     </row>
     <row r="159">
@@ -8695,41 +8851,45 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D159" t="n">
         <v>23</v>
       </c>
       <c r="E159" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
+        <v>3</v>
+      </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>0.0434782608695652</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
-      </c>
-      <c r="J159" t="inlineStr"/>
+        <v>0.0476190476190476</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0.0454545454545454</v>
+      </c>
       <c r="K159" t="n">
-        <v>0.9873417721518988</v>
+        <v>0.9877777777777778</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-11-19 00:00:00')]</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-11-16 00:00:00')]</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>0.9977495565739132</v>
+        <v>1.000022093113044</v>
       </c>
     </row>
     <row r="160">
@@ -8752,7 +8912,7 @@
         <v>20</v>
       </c>
       <c r="E160" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -8766,7 +8926,7 @@
       </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="n">
-        <v>0.9889928453494772</v>
+        <v>0.9889135254988912</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -8802,7 +8962,7 @@
         <v>18</v>
       </c>
       <c r="E161" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -8816,7 +8976,7 @@
       </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="n">
-        <v>0.9900826446280993</v>
+        <v>0.9900055524708496</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -8845,45 +9005,45 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E162" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F162" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G162" t="n">
-        <v>2.25</v>
+        <v>4.625</v>
       </c>
       <c r="H162" t="n">
-        <v>0.1</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="I162" t="n">
         <v>0.3076923076923077</v>
       </c>
       <c r="J162" t="n">
-        <v>0.1509433962264151</v>
+        <v>0.2</v>
       </c>
       <c r="K162" t="n">
-        <v>0.959866220735786</v>
+        <v>0.961257720381808</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2022-11-29 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2023-12-16 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-08 00:00:00'), Timestamp('2023-04-14 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-12-13 00:00:00')]</t>
+          <t>[Timestamp('2022-11-23 00:00:00'), Timestamp('2023-04-14 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-05-12 00:00:00'), Timestamp('2023-07-07 00:00:00'), Timestamp('2023-12-08 00:00:00'), Timestamp('2023-12-15 00:00:00'), Timestamp('2024-06-28 00:00:00')]</t>
         </is>
       </c>
       <c r="N162" t="n">
-        <v>0.99781452267125</v>
+        <v>0.9990972766246916</v>
       </c>
     </row>
     <row r="163">
@@ -8899,45 +9059,45 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E163" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F163" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G163" t="n">
-        <v>2.666666666666667</v>
+        <v>4.428571428571429</v>
       </c>
       <c r="H163" t="n">
-        <v>0.0842105263157894</v>
+        <v>0.1046511627906976</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="J163" t="n">
-        <v>0.134453781512605</v>
+        <v>0.15</v>
       </c>
       <c r="K163" t="n">
-        <v>0.951369480156512</v>
+        <v>0.9566929133858268</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-09 00:00:00'), Timestamp('2023-03-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-09-04 00:00:00'), Timestamp('2023-09-09 00:00:00')]</t>
+          <t>[Timestamp('2021-09-07 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-06-22 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-09-22 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-08 00:00:00'), Timestamp('2023-03-06 00:00:00'), Timestamp('2023-04-15 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-09-03 00:00:00'), Timestamp('2023-09-05 00:00:00')]</t>
+          <t>[Timestamp('2021-09-06 00:00:00'), Timestamp('2023-05-14 00:00:00'), Timestamp('2023-06-15 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-09-15 00:00:00'), Timestamp('2023-12-11 00:00:00'), Timestamp('2024-06-25 00:00:00')]</t>
         </is>
       </c>
       <c r="N163" t="n">
-        <v>0.999200921493684</v>
+        <v>0.9999479591383722</v>
       </c>
     </row>
     <row r="164">
@@ -8953,45 +9113,45 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E164" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F164" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G164" t="n">
-        <v>3.6</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0808080808080808</v>
+        <v>0.09473684210526311</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2571428571428571</v>
       </c>
       <c r="J164" t="n">
-        <v>0.1300813008130081</v>
+        <v>0.1384615384615384</v>
       </c>
       <c r="K164" t="n">
-        <v>0.9491620111731844</v>
+        <v>0.9516310461192352</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-07-24 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2022-11-29 00:00:00'), Timestamp('2023-03-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-09-04 00:00:00'), Timestamp('2023-09-09 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-08 00:00:00'), Timestamp('2023-04-15 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-07-19 00:00:00'), Timestamp('2023-12-09 00:00:00')]</t>
+          <t>[Timestamp('2022-11-28 00:00:00'), Timestamp('2023-03-06 00:00:00'), Timestamp('2023-04-15 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-09-03 00:00:00'), Timestamp('2023-09-05 00:00:00'), Timestamp('2024-06-27 00:00:00')]</t>
         </is>
       </c>
       <c r="N164" t="n">
-        <v>0.9996793000343436</v>
+        <v>0.999200921493684</v>
       </c>
     </row>
     <row r="165">
@@ -9007,45 +9167,45 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="E165" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F165" t="n">
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>2.571428571428572</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="H165" t="n">
-        <v>0.0792079207920792</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="J165" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.146788990825688</v>
       </c>
       <c r="K165" t="n">
-        <v>0.9481316229782488</v>
+        <v>0.9618406285072952</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-08-18 00:00:00'), Timestamp('2023-11-16 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2021-09-07 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-11-16 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2024-01-23 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-08 00:00:00'), Timestamp('2023-04-18 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-08-16 00:00:00'), Timestamp('2023-11-09 00:00:00'), Timestamp('2023-12-11 00:00:00')]</t>
+          <t>[Timestamp('2021-09-06 00:00:00'), Timestamp('2023-04-14 00:00:00'), Timestamp('2023-11-10 00:00:00'), Timestamp('2023-12-13 00:00:00'), Timestamp('2024-01-18 00:00:00'), Timestamp('2024-06-28 00:00:00')]</t>
         </is>
       </c>
       <c r="N165" t="n">
-        <v>0.9991614202970296</v>
+        <v>1.000012668840789</v>
       </c>
     </row>
     <row r="166">
@@ -9061,45 +9221,45 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="E166" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F166" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>4.2</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="H166" t="n">
-        <v>0.08641975308641971</v>
+        <v>0.0792079207920792</v>
       </c>
       <c r="I166" t="n">
-        <v>0.28</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="J166" t="n">
-        <v>0.1320754716981132</v>
+        <v>0.1185185185185185</v>
       </c>
       <c r="K166" t="n">
-        <v>0.9588202559821926</v>
+        <v>0.9478407178911946</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-14 00:00:00'), Timestamp('2023-12-14 00:00:00'), Timestamp('2023-12-16 00:00:00')]</t>
+          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-08-18 00:00:00'), Timestamp('2023-09-22 00:00:00'), Timestamp('2023-11-16 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-04-14 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-07-07 00:00:00'), Timestamp('2023-12-08 00:00:00'), Timestamp('2023-12-15 00:00:00')]</t>
+          <t>[Timestamp('2023-04-18 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-08-16 00:00:00'), Timestamp('2023-09-16 00:00:00'), Timestamp('2023-11-09 00:00:00'), Timestamp('2023-12-11 00:00:00')]</t>
         </is>
       </c>
       <c r="N166" t="n">
-        <v>0.9990972766246916</v>
+        <v>0.9991614202970296</v>
       </c>
     </row>
     <row r="167">
@@ -9115,45 +9275,45 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E167" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F167" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G167" t="n">
-        <v>3.5</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="H167" t="n">
-        <v>0.06578947368421049</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="I167" t="n">
-        <v>0.238095238095238</v>
+        <v>0.2058823529411764</v>
       </c>
       <c r="J167" t="n">
-        <v>0.1030927835051546</v>
+        <v>0.1228070175438596</v>
       </c>
       <c r="K167" t="n">
-        <v>0.9604677060133632</v>
+        <v>0.9591265397536394</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-07 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-11-16 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-06 00:00:00'), Timestamp('2023-04-14 00:00:00'), Timestamp('2023-11-10 00:00:00'), Timestamp('2023-12-13 00:00:00')]</t>
+          <t>[Timestamp('2023-04-14 00:00:00'), Timestamp('2023-05-03 00:00:00'), Timestamp('2023-12-13 00:00:00')]</t>
         </is>
       </c>
       <c r="N167" t="n">
-        <v>1.000012668840789</v>
+        <v>0.99781452267125</v>
       </c>
     </row>
     <row r="168">
@@ -9169,45 +9329,45 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E168" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F168" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G168" t="n">
-        <v>3.666666666666667</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="H168" t="n">
-        <v>0.0454545454545454</v>
+        <v>0.0707070707070707</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="J168" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.106060606060606</v>
       </c>
       <c r="K168" t="n">
-        <v>0.9532033426183844</v>
+        <v>0.9483436271757441</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00')]</t>
+          <t>[Timestamp('2023-03-09 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-07-21 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-13 00:00:00'), Timestamp('2023-04-14 00:00:00'), Timestamp('2023-05-03 00:00:00')]</t>
+          <t>[Timestamp('2023-03-08 00:00:00'), Timestamp('2023-04-15 00:00:00'), Timestamp('2023-05-14 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-07-20 00:00:00'), Timestamp('2023-12-09 00:00:00')]</t>
         </is>
       </c>
       <c r="N168" t="n">
-        <v>0.9997631552488636</v>
+        <v>0.9996793000343436</v>
       </c>
     </row>
     <row r="169">
@@ -9223,45 +9383,45 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E169" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F169" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G169" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="H169" t="n">
-        <v>0.0348837209302325</v>
+        <v>0.06818181818181809</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1621621621621621</v>
       </c>
       <c r="J169" t="n">
-        <v>0.0560747663551401</v>
+        <v>0.0959999999999999</v>
       </c>
       <c r="K169" t="n">
-        <v>0.9537861915367484</v>
+        <v>0.9539842873176206</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-07 00:00:00'), Timestamp('2023-07-03 00:00:00'), Timestamp('2023-12-14 00:00:00')]</t>
+          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2022-11-29 00:00:00'), Timestamp('2023-04-20 00:00:00'), Timestamp('2023-05-04 00:00:00')]</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-09-06 00:00:00'), Timestamp('2023-07-01 00:00:00'), Timestamp('2023-12-11 00:00:00')]</t>
+          <t>[Timestamp('2021-04-13 00:00:00'), Timestamp('2022-11-22 00:00:00'), Timestamp('2023-04-14 00:00:00'), Timestamp('2023-05-03 00:00:00')]</t>
         </is>
       </c>
       <c r="N169" t="n">
-        <v>0.9999479591383722</v>
+        <v>0.9997631552488636</v>
       </c>
     </row>
     <row r="170">
@@ -9284,34 +9444,34 @@
         <v>92</v>
       </c>
       <c r="E170" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G170" t="n">
-        <v>3</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="H170" t="n">
-        <v>0.0217391304347826</v>
+        <v>0.0652173913043478</v>
       </c>
       <c r="I170" t="n">
-        <v>0.0869565217391304</v>
+        <v>0.1621621621621621</v>
       </c>
       <c r="J170" t="n">
-        <v>0.0347826086956521</v>
+        <v>0.0930232558139534</v>
       </c>
       <c r="K170" t="n">
-        <v>0.9498886414253898</v>
+        <v>0.9517396184062852</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2021-09-09 00:00:00')]</t>
+          <t>[Timestamp('2021-04-17 00:00:00'), Timestamp('2023-05-19 00:00:00'), Timestamp('2024-07-01 00:00:00')]</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-12 00:00:00'), Timestamp('2021-09-08 00:00:00')]</t>
+          <t>[Timestamp('2021-04-12 00:00:00'), Timestamp('2023-05-12 00:00:00'), Timestamp('2024-06-29 00:00:00')]</t>
         </is>
       </c>
       <c r="N170" t="n">
@@ -9338,34 +9498,34 @@
         <v>93</v>
       </c>
       <c r="E171" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G171" t="n">
-        <v>3.5</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="H171" t="n">
-        <v>0.021505376344086</v>
+        <v>0.043010752688172</v>
       </c>
       <c r="I171" t="n">
-        <v>0.0869565217391304</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="J171" t="n">
-        <v>0.0344827586206896</v>
+        <v>0.0620155038759689</v>
       </c>
       <c r="K171" t="n">
-        <v>0.9493600445186422</v>
+        <v>0.950084127874369</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-09 00:00:00'), Timestamp('2023-08-18 00:00:00')]</t>
+          <t>[Timestamp('2023-03-09 00:00:00'), Timestamp('2023-06-22 00:00:00'), Timestamp('2023-08-18 00:00:00')]</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-03 00:00:00'), Timestamp('2023-08-17 00:00:00')]</t>
+          <t>[Timestamp('2023-03-03 00:00:00'), Timestamp('2023-06-19 00:00:00'), Timestamp('2023-08-17 00:00:00')]</t>
         </is>
       </c>
       <c r="N171" t="n">
@@ -9385,45 +9545,45 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E172" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H172" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="J172" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.2711864406779661</v>
       </c>
       <c r="K172" t="n">
-        <v>0.9922907488986784</v>
+        <v>0.9899272523782876</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2022-01-26 00:00:00'), Timestamp('2023-03-11 00:00:00'), Timestamp('2023-03-20 00:00:00')]</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-10 00:00:00')]</t>
+          <t>[Timestamp('2022-01-21 00:00:00'), Timestamp('2023-03-10 00:00:00'), Timestamp('2023-03-14 00:00:00')]</t>
         </is>
       </c>
       <c r="N172" t="n">
-        <v>0.9999012787533332</v>
+        <v>1.000484274907692</v>
       </c>
     </row>
     <row r="173">
@@ -9439,45 +9599,45 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E173" t="n">
+        <v>32</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" t="n">
         <v>3</v>
       </c>
-      <c r="F173" t="n">
-        <v>1</v>
-      </c>
-      <c r="G173" t="n">
-        <v>1</v>
-      </c>
       <c r="H173" t="n">
-        <v>0.0384615384615384</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>0.06451612903225799</v>
       </c>
       <c r="J173" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0869565217391304</v>
       </c>
       <c r="K173" t="n">
-        <v>0.9862410566868464</v>
+        <v>0.9927414852037968</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2021-06-26 00:00:00'), Timestamp('2021-12-05 00:00:00')]</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-10 00:00:00')]</t>
+          <t>[Timestamp('2021-06-21 00:00:00'), Timestamp('2021-12-04 00:00:00')]</t>
         </is>
       </c>
       <c r="N173" t="n">
-        <v>1.000484274907692</v>
+        <v>0.99995605376</v>
       </c>
     </row>
     <row r="174">
@@ -9493,41 +9653,45 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E174" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G174" t="n">
+        <v>3.5</v>
+      </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
-      </c>
-      <c r="J174" t="inlineStr"/>
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0.0888888888888888</v>
+      </c>
       <c r="K174" t="n">
-        <v>0.9928571428571428</v>
+        <v>0.9927414852037968</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-11-27 00:00:00'), Timestamp('2023-03-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-11-21 00:00:00'), Timestamp('2023-03-10 00:00:00')]</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>0.9985450312615384</v>
+        <v>0.9999012787533332</v>
       </c>
     </row>
     <row r="175">
@@ -9543,41 +9707,45 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E175" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G175" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G175" t="n">
+        <v>5</v>
+      </c>
       <c r="H175" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I175" t="n">
-        <v>0</v>
-      </c>
-      <c r="J175" t="inlineStr"/>
+        <v>0.0357142857142857</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0.0526315789473684</v>
+      </c>
       <c r="K175" t="n">
-        <v>0.987898789878988</v>
+        <v>0.9949804796430564</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-16 00:00:00')]</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-12-11 00:00:00')]</t>
         </is>
       </c>
       <c r="N175" t="n">
-        <v>0.9996994214363636</v>
+        <v>1.00046895461</v>
       </c>
     </row>
     <row r="176">
@@ -9593,41 +9761,45 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E176" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
       <c r="H176" t="n">
-        <v>0</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
-      </c>
-      <c r="J176" t="inlineStr"/>
+        <v>0.032258064516129</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0.0454545454545454</v>
+      </c>
       <c r="K176" t="n">
-        <v>0.991744634012108</v>
+        <v>0.9933035714285714</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-06-18 00:00:00')]</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-06-17 00:00:00')]</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>0.99995605376</v>
+        <v>1.000034873553846</v>
       </c>
     </row>
     <row r="177">
@@ -9643,14 +9815,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E177" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -9664,7 +9836,7 @@
       </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="n">
-        <v>0.9955971381397908</v>
+        <v>0.9927817878956136</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -9677,7 +9849,7 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>1.0000412935625</v>
+        <v>0.9985450312615384</v>
       </c>
     </row>
     <row r="178">
@@ -9693,14 +9865,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E178" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F178" t="n">
         <v>0</v>
@@ -9714,7 +9886,7 @@
       </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="n">
-        <v>0.9906439185470556</v>
+        <v>0.9877437325905292</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -9727,7 +9899,7 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>0.9999825692294116</v>
+        <v>0.9996994214363636</v>
       </c>
     </row>
     <row r="179">
@@ -9743,14 +9915,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E179" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F179" t="n">
         <v>0</v>
@@ -9764,7 +9936,7 @@
       </c>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="n">
-        <v>0.992294991744634</v>
+        <v>0.9955382041271612</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -9777,7 +9949,7 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>0.9999782151357144</v>
+        <v>1.0000412935625</v>
       </c>
     </row>
     <row r="180">
@@ -9793,14 +9965,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E180" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F180" t="n">
         <v>0</v>
@@ -9814,7 +9986,7 @@
       </c>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="n">
-        <v>0.9928453494771602</v>
+        <v>0.9905186837702176</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -9827,7 +9999,7 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>1.000034873553846</v>
+        <v>0.9999825692294116</v>
       </c>
     </row>
     <row r="181">
@@ -9843,14 +10015,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E181" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F181" t="n">
         <v>0</v>
@@ -9864,7 +10036,7 @@
       </c>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="n">
-        <v>0.9944964226747386</v>
+        <v>0.992191857222532</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -9877,7 +10049,7 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>1.00046895461</v>
+        <v>0.9999782151357144</v>
       </c>
     </row>
     <row r="182">
@@ -9893,45 +10065,45 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E182" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G182" t="n">
-        <v>7</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="H182" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="J182" t="n">
-        <v>0.125</v>
+        <v>0.1739130434782608</v>
       </c>
       <c r="K182" t="n">
-        <v>0.9928453494771602</v>
+        <v>0.992191857222532</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-17 00:00:00')]</t>
+          <t>[Timestamp('2022-05-11 00:00:00'), Timestamp('2022-11-10 00:00:00'), Timestamp('2026-02-04 00:00:00')]</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>[Timestamp('2021-04-10 00:00:00')]</t>
+          <t>[Timestamp('2022-05-08 00:00:00'), Timestamp('2022-11-08 00:00:00'), Timestamp('2026-01-30 00:00:00')]</t>
         </is>
       </c>
       <c r="N182" t="n">
-        <v>1.000142627692857</v>
+        <v>1.000001810805556</v>
       </c>
     </row>
     <row r="183">
@@ -9954,34 +10126,34 @@
         <v>15</v>
       </c>
       <c r="E183" t="n">
+        <v>28</v>
+      </c>
+      <c r="F183" t="n">
         <v>2</v>
-      </c>
-      <c r="F183" t="n">
-        <v>1</v>
       </c>
       <c r="G183" t="n">
         <v>1</v>
       </c>
       <c r="H183" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="J183" t="n">
         <v>0.1176470588235294</v>
       </c>
       <c r="K183" t="n">
-        <v>0.9922992299229924</v>
+        <v>0.992769744160178</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2022-05-11 00:00:00'), Timestamp('2022-11-10 00:00:00')]</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-10 00:00:00')]</t>
+          <t>[Timestamp('2022-05-10 00:00:00'), Timestamp('2022-11-09 00:00:00')]</t>
         </is>
       </c>
       <c r="N183" t="n">
@@ -10001,45 +10173,45 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E184" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F184" t="n">
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H184" t="n">
-        <v>0.0526315789473684</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5</v>
+        <v>0.0357142857142857</v>
       </c>
       <c r="J184" t="n">
-        <v>0.09523809523809521</v>
+        <v>0.048780487804878</v>
       </c>
       <c r="K184" t="n">
-        <v>0.9901044529961516</v>
+        <v>0.9933184855233852</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-11 00:00:00')]</t>
+          <t>[Timestamp('2021-04-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>[Timestamp('2023-03-10 00:00:00')]</t>
+          <t>[Timestamp('2021-04-08 00:00:00')]</t>
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1.000617961810526</v>
+        <v>1.000333382138461</v>
       </c>
     </row>
     <row r="185">
@@ -10055,41 +10227,45 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E185" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
-      </c>
-      <c r="G185" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1</v>
+      </c>
       <c r="H185" t="n">
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="I185" t="n">
-        <v>0</v>
-      </c>
-      <c r="J185" t="inlineStr"/>
+        <v>0.0454545454545454</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0.0555555555555555</v>
+      </c>
       <c r="K185" t="n">
-        <v>0.99009900990099</v>
+        <v>0.992769744160178</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-04-11 00:00:00')]</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2021-04-10 00:00:00')]</t>
         </is>
       </c>
       <c r="N185" t="n">
-        <v>1.000001810805556</v>
+        <v>1.000142627692857</v>
       </c>
     </row>
     <row r="186">
@@ -10105,41 +10281,45 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E186" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
-      </c>
-      <c r="G186" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G186" t="n">
+        <v>5</v>
+      </c>
       <c r="H186" t="n">
-        <v>0</v>
+        <v>0.0588235294117647</v>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
-      </c>
-      <c r="J186" t="inlineStr"/>
+        <v>0.0476190476190476</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0.0526315789473684</v>
+      </c>
       <c r="K186" t="n">
-        <v>0.9895489548954896</v>
+        <v>0.9911012235817576</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2026-02-04 00:00:00')]</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2026-01-30 00:00:00')]</t>
         </is>
       </c>
       <c r="N186" t="n">
-        <v>1.000193650573684</v>
+        <v>1.0007572734</v>
       </c>
     </row>
     <row r="187">
@@ -10155,41 +10335,45 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E187" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
-      </c>
-      <c r="G187" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
       <c r="H187" t="n">
-        <v>0</v>
+        <v>0.0526315789473684</v>
       </c>
       <c r="I187" t="n">
-        <v>0</v>
-      </c>
-      <c r="J187" t="inlineStr"/>
+        <v>0.0555555555555555</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0.054054054054054</v>
+      </c>
       <c r="K187" t="n">
-        <v>0.9911991199119912</v>
+        <v>0.9900166389351082</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-11-10 00:00:00')]</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-11-09 00:00:00')]</t>
         </is>
       </c>
       <c r="N187" t="n">
-        <v>1.00051355318125</v>
+        <v>1.000617961810526</v>
       </c>
     </row>
     <row r="188">
@@ -10205,41 +10389,45 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E188" t="n">
+        <v>28</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="n">
         <v>2</v>
       </c>
-      <c r="F188" t="n">
-        <v>0</v>
-      </c>
-      <c r="G188" t="inlineStr"/>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>0.0526315789473684</v>
       </c>
       <c r="I188" t="n">
-        <v>0</v>
-      </c>
-      <c r="J188" t="inlineStr"/>
+        <v>0.04</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0.0454545454545454</v>
+      </c>
       <c r="K188" t="n">
-        <v>0.9928492849284928</v>
+        <v>0.989983305509182</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-11-10 00:00:00')]</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-11-08 00:00:00')]</t>
         </is>
       </c>
       <c r="N188" t="n">
-        <v>1.000333382138461</v>
+        <v>1.000193650573684</v>
       </c>
     </row>
     <row r="189">
@@ -10255,14 +10443,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E189" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F189" t="n">
         <v>0</v>
@@ -10276,7 +10464,7 @@
       </c>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="n">
-        <v>0.9906490649064906</v>
+        <v>0.991106170094497</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -10289,7 +10477,7 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>1.0007572734</v>
+        <v>1.00051355318125</v>
       </c>
     </row>
     <row r="190">
@@ -10312,7 +10500,7 @@
         <v>13</v>
       </c>
       <c r="E190" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
@@ -10326,7 +10514,7 @@
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="n">
-        <v>0.9928492849284928</v>
+        <v>0.9927657206455204</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -10362,7 +10550,7 @@
         <v>12</v>
       </c>
       <c r="E191" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -10376,7 +10564,7 @@
       </c>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="n">
-        <v>0.9933993399339934</v>
+        <v>0.993322203672788</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -10412,7 +10600,7 @@
         <v>19</v>
       </c>
       <c r="E192" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F192" t="n">
         <v>5</v>
@@ -10424,13 +10612,13 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2272727272727272</v>
+        <v>0.1724137931034483</v>
       </c>
       <c r="J192" t="n">
-        <v>0.2439024390243902</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="K192" t="n">
-        <v>0.964824120603015</v>
+        <v>0.9645569620253164</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -10466,7 +10654,7 @@
         <v>23</v>
       </c>
       <c r="E193" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F193" t="n">
         <v>4</v>
@@ -10478,13 +10666,13 @@
         <v>0.1739130434782608</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="J193" t="n">
-        <v>0.1777777777777777</v>
+        <v>0.1568627450980392</v>
       </c>
       <c r="K193" t="n">
-        <v>0.9527363184079602</v>
+        <v>0.9522613065326632</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -10520,7 +10708,7 @@
         <v>13</v>
       </c>
       <c r="E194" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F194" t="n">
         <v>3</v>
@@ -10532,13 +10720,13 @@
         <v>0.2307692307692307</v>
       </c>
       <c r="I194" t="n">
-        <v>0.12</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="J194" t="n">
-        <v>0.1578947368421052</v>
+        <v>0.1363636363636363</v>
       </c>
       <c r="K194" t="n">
-        <v>0.9750623441396508</v>
+        <v>0.9748110831234256</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -10574,7 +10762,7 @@
         <v>16</v>
       </c>
       <c r="E195" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F195" t="n">
         <v>3</v>
@@ -10586,13 +10774,13 @@
         <v>0.1875</v>
       </c>
       <c r="I195" t="n">
+        <v>0.1071428571428571</v>
+      </c>
+      <c r="J195" t="n">
         <v>0.1363636363636363</v>
       </c>
-      <c r="J195" t="n">
-        <v>0.1578947368421052</v>
-      </c>
       <c r="K195" t="n">
-        <v>0.968058968058968</v>
+        <v>0.9678217821782178</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -10628,7 +10816,7 @@
         <v>17</v>
       </c>
       <c r="E196" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F196" t="n">
         <v>3</v>
@@ -10640,13 +10828,13 @@
         <v>0.1764705882352941</v>
       </c>
       <c r="I196" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="J196" t="n">
         <v>0.125</v>
       </c>
-      <c r="J196" t="n">
-        <v>0.1463414634146341</v>
-      </c>
       <c r="K196" t="n">
-        <v>0.9649122807017544</v>
+        <v>0.9645569620253164</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -10682,7 +10870,7 @@
         <v>18</v>
       </c>
       <c r="E197" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F197" t="n">
         <v>3</v>
@@ -10694,13 +10882,13 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1153846153846153</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="J197" t="n">
-        <v>0.1363636363636363</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="K197" t="n">
-        <v>0.962406015037594</v>
+        <v>0.9621212121212122</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -10736,7 +10924,7 @@
         <v>14</v>
       </c>
       <c r="E198" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F198" t="n">
         <v>2</v>
@@ -10748,13 +10936,13 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1</v>
+        <v>0.074074074074074</v>
       </c>
       <c r="J198" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.0975609756097561</v>
       </c>
       <c r="K198" t="n">
-        <v>0.9703703703703704</v>
+        <v>0.970074812967581</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -10783,41 +10971,45 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E199" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F199" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G199" t="n">
+        <v>7</v>
+      </c>
       <c r="H199" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I199" t="n">
-        <v>0</v>
-      </c>
-      <c r="J199" t="inlineStr"/>
+        <v>0.03125</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0.0384615384615384</v>
+      </c>
       <c r="K199" t="n">
-        <v>0.957920792079208</v>
+        <v>0.9521410579345088</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-03-04 00:00:00')]</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[Timestamp('2022-02-25 00:00:00')]</t>
         </is>
       </c>
       <c r="N199" t="n">
-        <v>0.9999851593941176</v>
+        <v>1.001144195575</v>
       </c>
     </row>
     <row r="200">
@@ -10833,14 +11025,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E200" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F200" t="n">
         <v>0</v>
@@ -10854,7 +11046,7 @@
       </c>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="n">
-        <v>0.9502487562189056</v>
+        <v>0.9575</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -10867,7 +11059,7 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>1.001144195575</v>
+        <v>0.9999851593941176</v>
       </c>
     </row>
     <row r="201">
@@ -10890,7 +11082,7 @@
         <v>16</v>
       </c>
       <c r="E201" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F201" t="n">
         <v>0</v>
@@ -10904,7 +11096,7 @@
       </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="n">
-        <v>0.9602977667493796</v>
+        <v>0.9598997493734336</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
